--- a/stations/output/SPE_Interlocking_Program.xlsx
+++ b/stations/output/SPE_Interlocking_Program.xlsx
@@ -1206,7 +1206,7 @@
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v0.21.0</t>
+          <t>v0.23.0</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="S6" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6, A2</t>
         </is>
       </c>
       <c r="T6" s="11" t="inlineStr"/>
@@ -1867,7 +1867,11 @@
           <t>8II</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr"/>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="N8" s="11" t="inlineStr"/>
       <c r="O8" s="12" t="inlineStr"/>
       <c r="P8" s="11" t="inlineStr"/>
@@ -2007,7 +2011,7 @@
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr">
         <is>
-          <t>8II</t>
+          <t>8II, 8I</t>
         </is>
       </c>
       <c r="N10" s="11" t="inlineStr"/>
@@ -2443,7 +2447,7 @@
       </c>
       <c r="S16" s="12" t="inlineStr">
         <is>
-          <t>1II/3II</t>
+          <t>1II/3II, 1I</t>
         </is>
       </c>
       <c r="T16" s="11" t="inlineStr"/>
@@ -2522,7 +2526,7 @@
       </c>
       <c r="S17" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 3I</t>
+          <t>1II/3II, 3I, D4</t>
         </is>
       </c>
       <c r="T17" s="11" t="inlineStr"/>
@@ -2826,7 +2830,7 @@
       </c>
       <c r="S21" s="12" t="inlineStr">
         <is>
-          <t>1II/3II</t>
+          <t>1II/3II, 1I</t>
         </is>
       </c>
       <c r="T21" s="11" t="inlineStr"/>
@@ -2905,7 +2909,7 @@
       </c>
       <c r="S22" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 3I</t>
+          <t>1II/3II, 3I, D4</t>
         </is>
       </c>
       <c r="T22" s="11" t="inlineStr"/>
@@ -3030,7 +3034,11 @@
           <t>2I, 2II</t>
         </is>
       </c>
-      <c r="L24" s="11" t="inlineStr"/>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="M24" s="12" t="inlineStr"/>
       <c r="N24" s="11" t="inlineStr"/>
       <c r="O24" s="12" t="inlineStr"/>
@@ -3043,7 +3051,7 @@
       </c>
       <c r="S24" s="12" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>1I, A1</t>
         </is>
       </c>
       <c r="T24" s="11" t="inlineStr"/>
@@ -9521,7 +9529,11 @@
           <t>8II</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr"/>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="N6" s="11" t="inlineStr"/>
       <c r="O6" s="12" t="inlineStr"/>
       <c r="P6" s="11" t="inlineStr"/>
@@ -9653,7 +9665,7 @@
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr">
         <is>
-          <t>8II</t>
+          <t>8II, 8I</t>
         </is>
       </c>
       <c r="N8" s="11" t="inlineStr"/>
@@ -9797,7 +9809,7 @@
       </c>
       <c r="S10" s="12" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>8I, D3</t>
         </is>
       </c>
       <c r="T10" s="11" t="inlineStr"/>
@@ -10215,7 +10227,7 @@
       </c>
       <c r="S16" s="12" t="inlineStr">
         <is>
-          <t>1II/3II</t>
+          <t>1II/3II, 1I</t>
         </is>
       </c>
       <c r="T16" s="11" t="inlineStr"/>
@@ -10294,7 +10306,7 @@
       </c>
       <c r="S17" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 3I</t>
+          <t>1II/3II, 3I, D4</t>
         </is>
       </c>
       <c r="T17" s="11" t="inlineStr"/>
@@ -10598,7 +10610,7 @@
       </c>
       <c r="S21" s="12" t="inlineStr">
         <is>
-          <t>1II/3II</t>
+          <t>1II/3II, 1I</t>
         </is>
       </c>
       <c r="T21" s="11" t="inlineStr"/>
@@ -10677,7 +10689,7 @@
       </c>
       <c r="S22" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 3I</t>
+          <t>1II/3II, 3I, D4</t>
         </is>
       </c>
       <c r="T22" s="11" t="inlineStr"/>
@@ -10798,7 +10810,11 @@
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr"/>
-      <c r="L24" s="11" t="inlineStr"/>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="M24" s="12" t="inlineStr"/>
       <c r="N24" s="11" t="inlineStr"/>
       <c r="O24" s="12" t="inlineStr"/>
@@ -10811,7 +10827,7 @@
       </c>
       <c r="S24" s="12" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>1I, A1</t>
         </is>
       </c>
       <c r="T24" s="11" t="inlineStr"/>
@@ -24999,7 +25015,7 @@
       </c>
       <c r="C8" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">main_ol_distance 120
+          <t xml:space="preserve">main_ol_distance 150
 </t>
         </is>
       </c>

--- a/stations/output/SPE_Interlocking_Program.xlsx
+++ b/stations/output/SPE_Interlocking_Program.xlsx
@@ -1206,7 +1206,7 @@
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v0.23.0</t>
+          <t>v0.24.1</t>
         </is>
       </c>
     </row>
@@ -1738,10 +1738,18 @@
         </is>
       </c>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
       <c r="O6" s="12" t="inlineStr"/>
       <c r="P6" s="11" t="inlineStr"/>
-      <c r="Q6" s="12" t="inlineStr"/>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="R6" s="11" t="inlineStr">
         <is>
           <t>A1, 1I, I</t>
@@ -1749,13 +1757,17 @@
       </c>
       <c r="S6" s="12" t="inlineStr">
         <is>
-          <t>6, A2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="T6" s="11" t="inlineStr"/>
       <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
-      <c r="W6" s="12" t="inlineStr"/>
+      <c r="W6" s="12" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="X6" s="11" t="inlineStr"/>
       <c r="Y6" s="12" t="inlineStr"/>
       <c r="Z6" s="11" t="inlineStr"/>
@@ -1801,16 +1813,28 @@
       <c r="K7" s="12" t="inlineStr"/>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
       <c r="O7" s="12" t="inlineStr"/>
       <c r="P7" s="11" t="inlineStr"/>
-      <c r="Q7" s="12" t="inlineStr"/>
+      <c r="Q7" s="12" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
       <c r="T7" s="11" t="inlineStr"/>
       <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
-      <c r="W7" s="12" t="inlineStr"/>
+      <c r="W7" s="12" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="X7" s="11" t="inlineStr"/>
       <c r="Y7" s="12" t="inlineStr"/>
       <c r="Z7" s="11" t="inlineStr"/>
@@ -1867,14 +1891,14 @@
           <t>8II</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="M8" s="12" t="inlineStr"/>
       <c r="N8" s="11" t="inlineStr"/>
       <c r="O8" s="12" t="inlineStr"/>
-      <c r="P8" s="11" t="inlineStr"/>
+      <c r="P8" s="11" t="inlineStr">
+        <is>
+          <t>8I</t>
+        </is>
+      </c>
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr">
         <is>
@@ -1886,7 +1910,11 @@
           <t>8II, 6</t>
         </is>
       </c>
-      <c r="T8" s="11" t="inlineStr"/>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="U8" s="12" t="inlineStr"/>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
@@ -1949,11 +1977,19 @@
       <c r="M9" s="12" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr"/>
       <c r="O9" s="12" t="inlineStr"/>
-      <c r="P9" s="11" t="inlineStr"/>
+      <c r="P9" s="11" t="inlineStr">
+        <is>
+          <t>8I</t>
+        </is>
+      </c>
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr"/>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="U9" s="12" t="inlineStr"/>
       <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
@@ -2011,12 +2047,16 @@
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr">
         <is>
-          <t>8II, 8I</t>
+          <t>8II</t>
         </is>
       </c>
       <c r="N10" s="11" t="inlineStr"/>
       <c r="O10" s="12" t="inlineStr"/>
-      <c r="P10" s="11" t="inlineStr"/>
+      <c r="P10" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr">
         <is>
@@ -2028,7 +2068,11 @@
           <t>8II, 8I</t>
         </is>
       </c>
-      <c r="T10" s="11" t="inlineStr"/>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="U10" s="12" t="inlineStr"/>
       <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
@@ -2091,11 +2135,19 @@
       </c>
       <c r="N11" s="11" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr"/>
-      <c r="P11" s="11" t="inlineStr"/>
+      <c r="P11" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr"/>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="U11" s="12" t="inlineStr"/>
       <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="12" t="inlineStr"/>
@@ -2148,9 +2200,17 @@
         </is>
       </c>
       <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>4II, 8II</t>
+        </is>
+      </c>
       <c r="O12" s="12" t="inlineStr"/>
-      <c r="P12" s="11" t="inlineStr"/>
+      <c r="P12" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr">
         <is>
@@ -2162,10 +2222,22 @@
           <t>3I, D4</t>
         </is>
       </c>
-      <c r="T12" s="11" t="inlineStr"/>
-      <c r="U12" s="12" t="inlineStr"/>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>2II, 4I, 4I</t>
+        </is>
+      </c>
+      <c r="U12" s="12" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="V12" s="11" t="inlineStr"/>
-      <c r="W12" s="12" t="inlineStr"/>
+      <c r="W12" s="12" t="inlineStr">
+        <is>
+          <t>1II/3II</t>
+        </is>
+      </c>
       <c r="X12" s="11" t="inlineStr"/>
       <c r="Y12" s="12" t="inlineStr"/>
       <c r="Z12" s="11" t="inlineStr"/>
@@ -2211,16 +2283,36 @@
       <c r="K13" s="12" t="inlineStr"/>
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr"/>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>4II, 8II</t>
+        </is>
+      </c>
       <c r="O13" s="12" t="inlineStr"/>
-      <c r="P13" s="11" t="inlineStr"/>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
-      <c r="T13" s="11" t="inlineStr"/>
-      <c r="U13" s="12" t="inlineStr"/>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>2II, 4I, 4I</t>
+        </is>
+      </c>
+      <c r="U13" s="12" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="V13" s="11" t="inlineStr"/>
-      <c r="W13" s="12" t="inlineStr"/>
+      <c r="W13" s="12" t="inlineStr">
+        <is>
+          <t>1II/3II</t>
+        </is>
+      </c>
       <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
       <c r="Z13" s="11" t="inlineStr"/>
@@ -2282,9 +2374,17 @@
         </is>
       </c>
       <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="11" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>4II, 6</t>
+        </is>
+      </c>
       <c r="O14" s="12" t="inlineStr"/>
-      <c r="P14" s="11" t="inlineStr"/>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr">
         <is>
@@ -2296,11 +2396,27 @@
           <t>1II/3II</t>
         </is>
       </c>
-      <c r="T14" s="11" t="inlineStr"/>
-      <c r="U14" s="12" t="inlineStr"/>
+      <c r="T14" s="11" t="inlineStr">
+        <is>
+          <t>2II, 4I, 4I</t>
+        </is>
+      </c>
+      <c r="U14" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="V14" s="11" t="inlineStr"/>
-      <c r="W14" s="12" t="inlineStr"/>
-      <c r="X14" s="11" t="inlineStr"/>
+      <c r="W14" s="12" t="inlineStr">
+        <is>
+          <t>3I, 1I</t>
+        </is>
+      </c>
+      <c r="X14" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y14" s="12" t="inlineStr"/>
       <c r="Z14" s="11" t="inlineStr"/>
       <c r="AA14" s="13" t="inlineStr"/>
@@ -2361,17 +2477,41 @@
         </is>
       </c>
       <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>4II, 6</t>
+        </is>
+      </c>
       <c r="O15" s="12" t="inlineStr"/>
-      <c r="P15" s="11" t="inlineStr"/>
+      <c r="P15" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr"/>
-      <c r="U15" s="12" t="inlineStr"/>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>2II, 4I, 4I</t>
+        </is>
+      </c>
+      <c r="U15" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="V15" s="11" t="inlineStr"/>
-      <c r="W15" s="12" t="inlineStr"/>
-      <c r="X15" s="11" t="inlineStr"/>
+      <c r="W15" s="12" t="inlineStr">
+        <is>
+          <t>3I, 1I</t>
+        </is>
+      </c>
+      <c r="X15" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y15" s="12" t="inlineStr"/>
       <c r="Z15" s="11" t="inlineStr"/>
       <c r="AA15" s="13" t="inlineStr"/>
@@ -2436,7 +2576,11 @@
           <t>1II</t>
         </is>
       </c>
-      <c r="N16" s="11" t="inlineStr"/>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>4II, 6</t>
+        </is>
+      </c>
       <c r="O16" s="12" t="inlineStr"/>
       <c r="P16" s="11" t="inlineStr"/>
       <c r="Q16" s="12" t="inlineStr"/>
@@ -2447,13 +2591,25 @@
       </c>
       <c r="S16" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 1I</t>
-        </is>
-      </c>
-      <c r="T16" s="11" t="inlineStr"/>
-      <c r="U16" s="12" t="inlineStr"/>
+          <t>1II/3II</t>
+        </is>
+      </c>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>2II, 4I, 4I</t>
+        </is>
+      </c>
+      <c r="U16" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="V16" s="11" t="inlineStr"/>
-      <c r="W16" s="12" t="inlineStr"/>
+      <c r="W16" s="12" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="X16" s="11" t="inlineStr"/>
       <c r="Y16" s="12" t="inlineStr"/>
       <c r="Z16" s="11" t="inlineStr"/>
@@ -2515,9 +2671,17 @@
           <t>3II, 3I</t>
         </is>
       </c>
-      <c r="N17" s="11" t="inlineStr"/>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>4II, 6</t>
+        </is>
+      </c>
       <c r="O17" s="12" t="inlineStr"/>
-      <c r="P17" s="11" t="inlineStr"/>
+      <c r="P17" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr">
         <is>
@@ -2526,14 +2690,30 @@
       </c>
       <c r="S17" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 3I, D4</t>
-        </is>
-      </c>
-      <c r="T17" s="11" t="inlineStr"/>
-      <c r="U17" s="12" t="inlineStr"/>
+          <t>1II/3II, 3I</t>
+        </is>
+      </c>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>2II, 4I, 4I</t>
+        </is>
+      </c>
+      <c r="U17" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="V17" s="11" t="inlineStr"/>
-      <c r="W17" s="12" t="inlineStr"/>
-      <c r="X17" s="11" t="inlineStr"/>
+      <c r="W17" s="12" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="X17" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y17" s="12" t="inlineStr"/>
       <c r="Z17" s="11" t="inlineStr"/>
       <c r="AA17" s="13" t="inlineStr"/>
@@ -2594,17 +2774,41 @@
           <t>3II</t>
         </is>
       </c>
-      <c r="N18" s="11" t="inlineStr"/>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>4II, 6</t>
+        </is>
+      </c>
       <c r="O18" s="12" t="inlineStr"/>
-      <c r="P18" s="11" t="inlineStr"/>
+      <c r="P18" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="11" t="inlineStr"/>
       <c r="S18" s="12" t="inlineStr"/>
-      <c r="T18" s="11" t="inlineStr"/>
-      <c r="U18" s="12" t="inlineStr"/>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>2II, 4I, 4I</t>
+        </is>
+      </c>
+      <c r="U18" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="V18" s="11" t="inlineStr"/>
-      <c r="W18" s="12" t="inlineStr"/>
-      <c r="X18" s="11" t="inlineStr"/>
+      <c r="W18" s="12" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="X18" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y18" s="12" t="inlineStr"/>
       <c r="Z18" s="11" t="inlineStr"/>
       <c r="AA18" s="13" t="inlineStr"/>
@@ -2665,9 +2869,17 @@
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="11" t="inlineStr"/>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>8II, 8I</t>
+        </is>
+      </c>
       <c r="O19" s="12" t="inlineStr"/>
-      <c r="P19" s="11" t="inlineStr"/>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q19" s="12" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
@@ -2679,11 +2891,27 @@
           <t>1II/3II</t>
         </is>
       </c>
-      <c r="T19" s="11" t="inlineStr"/>
-      <c r="U19" s="12" t="inlineStr"/>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>4II, 8I</t>
+        </is>
+      </c>
+      <c r="U19" s="12" t="inlineStr">
+        <is>
+          <t>A3, D3</t>
+        </is>
+      </c>
       <c r="V19" s="11" t="inlineStr"/>
-      <c r="W19" s="12" t="inlineStr"/>
-      <c r="X19" s="11" t="inlineStr"/>
+      <c r="W19" s="12" t="inlineStr">
+        <is>
+          <t>3I, 1I</t>
+        </is>
+      </c>
+      <c r="X19" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y19" s="12" t="inlineStr"/>
       <c r="Z19" s="11" t="inlineStr"/>
       <c r="AA19" s="13" t="inlineStr"/>
@@ -2744,17 +2972,41 @@
         </is>
       </c>
       <c r="M20" s="12" t="inlineStr"/>
-      <c r="N20" s="11" t="inlineStr"/>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>8II, 8I</t>
+        </is>
+      </c>
       <c r="O20" s="12" t="inlineStr"/>
-      <c r="P20" s="11" t="inlineStr"/>
+      <c r="P20" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q20" s="12" t="inlineStr"/>
       <c r="R20" s="11" t="inlineStr"/>
       <c r="S20" s="12" t="inlineStr"/>
-      <c r="T20" s="11" t="inlineStr"/>
-      <c r="U20" s="12" t="inlineStr"/>
+      <c r="T20" s="11" t="inlineStr">
+        <is>
+          <t>4II, 8I</t>
+        </is>
+      </c>
+      <c r="U20" s="12" t="inlineStr">
+        <is>
+          <t>A3, D3</t>
+        </is>
+      </c>
       <c r="V20" s="11" t="inlineStr"/>
-      <c r="W20" s="12" t="inlineStr"/>
-      <c r="X20" s="11" t="inlineStr"/>
+      <c r="W20" s="12" t="inlineStr">
+        <is>
+          <t>3I, 1I</t>
+        </is>
+      </c>
+      <c r="X20" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y20" s="12" t="inlineStr"/>
       <c r="Z20" s="11" t="inlineStr"/>
       <c r="AA20" s="13" t="inlineStr"/>
@@ -2819,7 +3071,11 @@
           <t>1II</t>
         </is>
       </c>
-      <c r="N21" s="11" t="inlineStr"/>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>8II, 8I</t>
+        </is>
+      </c>
       <c r="O21" s="12" t="inlineStr"/>
       <c r="P21" s="11" t="inlineStr"/>
       <c r="Q21" s="12" t="inlineStr"/>
@@ -2830,13 +3086,25 @@
       </c>
       <c r="S21" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 1I</t>
-        </is>
-      </c>
-      <c r="T21" s="11" t="inlineStr"/>
-      <c r="U21" s="12" t="inlineStr"/>
+          <t>1II/3II</t>
+        </is>
+      </c>
+      <c r="T21" s="11" t="inlineStr">
+        <is>
+          <t>4II, 8I</t>
+        </is>
+      </c>
+      <c r="U21" s="12" t="inlineStr">
+        <is>
+          <t>A3, D3</t>
+        </is>
+      </c>
       <c r="V21" s="11" t="inlineStr"/>
-      <c r="W21" s="12" t="inlineStr"/>
+      <c r="W21" s="12" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="X21" s="11" t="inlineStr"/>
       <c r="Y21" s="12" t="inlineStr"/>
       <c r="Z21" s="11" t="inlineStr"/>
@@ -2898,9 +3166,17 @@
           <t>3II, 3I</t>
         </is>
       </c>
-      <c r="N22" s="11" t="inlineStr"/>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>8II, 8I</t>
+        </is>
+      </c>
       <c r="O22" s="12" t="inlineStr"/>
-      <c r="P22" s="11" t="inlineStr"/>
+      <c r="P22" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q22" s="12" t="inlineStr"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
@@ -2909,14 +3185,30 @@
       </c>
       <c r="S22" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 3I, D4</t>
-        </is>
-      </c>
-      <c r="T22" s="11" t="inlineStr"/>
-      <c r="U22" s="12" t="inlineStr"/>
+          <t>1II/3II, 3I</t>
+        </is>
+      </c>
+      <c r="T22" s="11" t="inlineStr">
+        <is>
+          <t>4II, 8I</t>
+        </is>
+      </c>
+      <c r="U22" s="12" t="inlineStr">
+        <is>
+          <t>A3, D3</t>
+        </is>
+      </c>
       <c r="V22" s="11" t="inlineStr"/>
-      <c r="W22" s="12" t="inlineStr"/>
-      <c r="X22" s="11" t="inlineStr"/>
+      <c r="W22" s="12" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="X22" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y22" s="12" t="inlineStr"/>
       <c r="Z22" s="11" t="inlineStr"/>
       <c r="AA22" s="13" t="inlineStr"/>
@@ -2977,17 +3269,41 @@
           <t>3II</t>
         </is>
       </c>
-      <c r="N23" s="11" t="inlineStr"/>
+      <c r="N23" s="11" t="inlineStr">
+        <is>
+          <t>8II, 8I</t>
+        </is>
+      </c>
       <c r="O23" s="12" t="inlineStr"/>
-      <c r="P23" s="11" t="inlineStr"/>
+      <c r="P23" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q23" s="12" t="inlineStr"/>
       <c r="R23" s="11" t="inlineStr"/>
       <c r="S23" s="12" t="inlineStr"/>
-      <c r="T23" s="11" t="inlineStr"/>
-      <c r="U23" s="12" t="inlineStr"/>
+      <c r="T23" s="11" t="inlineStr">
+        <is>
+          <t>4II, 8I</t>
+        </is>
+      </c>
+      <c r="U23" s="12" t="inlineStr">
+        <is>
+          <t>A3, D3</t>
+        </is>
+      </c>
       <c r="V23" s="11" t="inlineStr"/>
-      <c r="W23" s="12" t="inlineStr"/>
-      <c r="X23" s="11" t="inlineStr"/>
+      <c r="W23" s="12" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="X23" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y23" s="12" t="inlineStr"/>
       <c r="Z23" s="11" t="inlineStr"/>
       <c r="AA23" s="13" t="inlineStr"/>
@@ -3034,15 +3350,19 @@
           <t>2I, 2II</t>
         </is>
       </c>
-      <c r="L24" s="11" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="L24" s="11" t="inlineStr"/>
       <c r="M24" s="12" t="inlineStr"/>
-      <c r="N24" s="11" t="inlineStr"/>
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="O24" s="12" t="inlineStr"/>
-      <c r="P24" s="11" t="inlineStr"/>
+      <c r="P24" s="11" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
       <c r="Q24" s="12" t="inlineStr"/>
       <c r="R24" s="11" t="inlineStr">
         <is>
@@ -3051,13 +3371,25 @@
       </c>
       <c r="S24" s="12" t="inlineStr">
         <is>
-          <t>1I, A1</t>
-        </is>
-      </c>
-      <c r="T24" s="11" t="inlineStr"/>
-      <c r="U24" s="12" t="inlineStr"/>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="T24" s="11" t="inlineStr">
+        <is>
+          <t>4II, 8II</t>
+        </is>
+      </c>
+      <c r="U24" s="12" t="inlineStr">
+        <is>
+          <t>A3, D3</t>
+        </is>
+      </c>
       <c r="V24" s="11" t="inlineStr"/>
-      <c r="W24" s="12" t="inlineStr"/>
+      <c r="W24" s="12" t="inlineStr">
+        <is>
+          <t>1II/3II</t>
+        </is>
+      </c>
       <c r="X24" s="11" t="inlineStr"/>
       <c r="Y24" s="12" t="inlineStr"/>
       <c r="Z24" s="11" t="inlineStr"/>
@@ -3107,16 +3439,36 @@
       </c>
       <c r="L25" s="11" t="inlineStr"/>
       <c r="M25" s="12" t="inlineStr"/>
-      <c r="N25" s="11" t="inlineStr"/>
+      <c r="N25" s="11" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="O25" s="12" t="inlineStr"/>
-      <c r="P25" s="11" t="inlineStr"/>
+      <c r="P25" s="11" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
       <c r="Q25" s="12" t="inlineStr"/>
       <c r="R25" s="11" t="inlineStr"/>
       <c r="S25" s="12" t="inlineStr"/>
-      <c r="T25" s="11" t="inlineStr"/>
-      <c r="U25" s="12" t="inlineStr"/>
+      <c r="T25" s="11" t="inlineStr">
+        <is>
+          <t>4II, 8II</t>
+        </is>
+      </c>
+      <c r="U25" s="12" t="inlineStr">
+        <is>
+          <t>A3, D3</t>
+        </is>
+      </c>
       <c r="V25" s="11" t="inlineStr"/>
-      <c r="W25" s="12" t="inlineStr"/>
+      <c r="W25" s="12" t="inlineStr">
+        <is>
+          <t>1II/3II</t>
+        </is>
+      </c>
       <c r="X25" s="11" t="inlineStr"/>
       <c r="Y25" s="12" t="inlineStr"/>
       <c r="Z25" s="11" t="inlineStr"/>
@@ -5841,7 +6193,11 @@
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
       <c r="N6" s="11" t="inlineStr"/>
-      <c r="O6" s="12" t="inlineStr"/>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr">
@@ -5850,8 +6206,16 @@
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr"/>
-      <c r="U6" s="12" t="inlineStr"/>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>4II, 2I</t>
+        </is>
+      </c>
+      <c r="U6" s="12" t="inlineStr">
+        <is>
+          <t>D3, D1</t>
+        </is>
+      </c>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
@@ -5904,13 +6268,25 @@
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr"/>
-      <c r="O7" s="12" t="inlineStr"/>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="P7" s="11" t="inlineStr"/>
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr"/>
-      <c r="U7" s="12" t="inlineStr"/>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>4II, 2I</t>
+        </is>
+      </c>
+      <c r="U7" s="12" t="inlineStr">
+        <is>
+          <t>D3, D1</t>
+        </is>
+      </c>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
@@ -5970,7 +6346,11 @@
       </c>
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>8I, 8II</t>
+        </is>
+      </c>
       <c r="O8" s="12" t="inlineStr"/>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
@@ -5980,8 +6360,16 @@
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr"/>
-      <c r="U8" s="12" t="inlineStr"/>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>4II, 2I</t>
+        </is>
+      </c>
+      <c r="U8" s="12" t="inlineStr">
+        <is>
+          <t>D3, D1</t>
+        </is>
+      </c>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
       <c r="X8" s="11" t="inlineStr"/>
@@ -6041,14 +6429,26 @@
       </c>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>8I, 8II</t>
+        </is>
+      </c>
       <c r="O9" s="12" t="inlineStr"/>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr"/>
-      <c r="U9" s="12" t="inlineStr"/>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>4II, 2I</t>
+        </is>
+      </c>
+      <c r="U9" s="12" t="inlineStr">
+        <is>
+          <t>D3, D1</t>
+        </is>
+      </c>
       <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
       <c r="X9" s="11" t="inlineStr"/>
@@ -6108,8 +6508,16 @@
       </c>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
-      <c r="O10" s="12" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>2I, 8II</t>
+        </is>
+      </c>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr">
@@ -6118,9 +6526,21 @@
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr"/>
-      <c r="U10" s="12" t="inlineStr"/>
-      <c r="V10" s="11" t="inlineStr"/>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>2I, 2I</t>
+        </is>
+      </c>
+      <c r="U10" s="12" t="inlineStr">
+        <is>
+          <t>A2, D1</t>
+        </is>
+      </c>
+      <c r="V10" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
       <c r="Y10" s="12" t="inlineStr"/>
@@ -6179,15 +6599,35 @@
       </c>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
-      <c r="O11" s="12" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>2I, 8II</t>
+        </is>
+      </c>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr"/>
-      <c r="U11" s="12" t="inlineStr"/>
-      <c r="V11" s="11" t="inlineStr"/>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>2I, 2I</t>
+        </is>
+      </c>
+      <c r="U11" s="12" t="inlineStr">
+        <is>
+          <t>A2, D1</t>
+        </is>
+      </c>
+      <c r="V11" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="11" t="inlineStr"/>
       <c r="Y11" s="12" t="inlineStr"/>
@@ -6242,8 +6682,16 @@
       </c>
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="11" t="inlineStr"/>
-      <c r="O12" s="12" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>2I, 8II</t>
+        </is>
+      </c>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr">
@@ -6252,9 +6700,21 @@
         </is>
       </c>
       <c r="S12" s="12" t="inlineStr"/>
-      <c r="T12" s="11" t="inlineStr"/>
-      <c r="U12" s="12" t="inlineStr"/>
-      <c r="V12" s="11" t="inlineStr"/>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>2I, 2I</t>
+        </is>
+      </c>
+      <c r="U12" s="12" t="inlineStr">
+        <is>
+          <t>A2, D1</t>
+        </is>
+      </c>
+      <c r="V12" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="W12" s="12" t="inlineStr"/>
       <c r="X12" s="11" t="inlineStr"/>
       <c r="Y12" s="12" t="inlineStr"/>
@@ -6309,15 +6769,35 @@
       </c>
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr"/>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>2I, 8II</t>
+        </is>
+      </c>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
-      <c r="T13" s="11" t="inlineStr"/>
-      <c r="U13" s="12" t="inlineStr"/>
-      <c r="V13" s="11" t="inlineStr"/>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>2I, 2I</t>
+        </is>
+      </c>
+      <c r="U13" s="12" t="inlineStr">
+        <is>
+          <t>A2, D1</t>
+        </is>
+      </c>
+      <c r="V13" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="W13" s="12" t="inlineStr"/>
       <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
@@ -6368,7 +6848,11 @@
       <c r="K14" s="12" t="inlineStr"/>
       <c r="L14" s="11" t="inlineStr"/>
       <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="11" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="O14" s="12" t="inlineStr"/>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -6431,7 +6915,11 @@
       <c r="K15" s="12" t="inlineStr"/>
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="O15" s="12" t="inlineStr"/>
       <c r="P15" s="11" t="inlineStr"/>
       <c r="Q15" s="12" t="inlineStr"/>
@@ -6490,7 +6978,11 @@
       </c>
       <c r="L16" s="11" t="inlineStr"/>
       <c r="M16" s="12" t="inlineStr"/>
-      <c r="N16" s="11" t="inlineStr"/>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="O16" s="12" t="inlineStr"/>
       <c r="P16" s="11" t="inlineStr"/>
       <c r="Q16" s="12" t="inlineStr"/>
@@ -6553,7 +7045,11 @@
       </c>
       <c r="L17" s="11" t="inlineStr"/>
       <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="11" t="inlineStr"/>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="O17" s="12" t="inlineStr"/>
       <c r="P17" s="11" t="inlineStr"/>
       <c r="Q17" s="12" t="inlineStr"/>
@@ -9529,14 +10025,18 @@
           <t>8II</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N6" s="11" t="inlineStr"/>
+      <c r="M6" s="12" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="O6" s="12" t="inlineStr"/>
-      <c r="P6" s="11" t="inlineStr"/>
+      <c r="P6" s="11" t="inlineStr">
+        <is>
+          <t>8I</t>
+        </is>
+      </c>
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr">
         <is>
@@ -9551,7 +10051,11 @@
       <c r="T6" s="11" t="inlineStr"/>
       <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
-      <c r="W6" s="12" t="inlineStr"/>
+      <c r="W6" s="12" t="inlineStr">
+        <is>
+          <t>8I</t>
+        </is>
+      </c>
       <c r="X6" s="11" t="inlineStr"/>
       <c r="Y6" s="12" t="inlineStr"/>
       <c r="Z6" s="11" t="inlineStr"/>
@@ -9605,16 +10109,28 @@
         </is>
       </c>
       <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="O7" s="12" t="inlineStr"/>
-      <c r="P7" s="11" t="inlineStr"/>
+      <c r="P7" s="11" t="inlineStr">
+        <is>
+          <t>8I</t>
+        </is>
+      </c>
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
       <c r="T7" s="11" t="inlineStr"/>
       <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
-      <c r="W7" s="12" t="inlineStr"/>
+      <c r="W7" s="12" t="inlineStr">
+        <is>
+          <t>8I</t>
+        </is>
+      </c>
       <c r="X7" s="11" t="inlineStr"/>
       <c r="Y7" s="12" t="inlineStr"/>
       <c r="Z7" s="11" t="inlineStr"/>
@@ -9665,12 +10181,20 @@
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr">
         <is>
-          <t>8II, 8I</t>
-        </is>
-      </c>
-      <c r="N8" s="11" t="inlineStr"/>
+          <t>8II</t>
+        </is>
+      </c>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="O8" s="12" t="inlineStr"/>
-      <c r="P8" s="11" t="inlineStr"/>
+      <c r="P8" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr">
         <is>
@@ -9686,7 +10210,11 @@
       <c r="U8" s="12" t="inlineStr"/>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
-      <c r="X8" s="11" t="inlineStr"/>
+      <c r="X8" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y8" s="12" t="inlineStr"/>
       <c r="Z8" s="11" t="inlineStr"/>
       <c r="AA8" s="13" t="inlineStr"/>
@@ -9739,9 +10267,17 @@
           <t>8II</t>
         </is>
       </c>
-      <c r="N9" s="11" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="O9" s="12" t="inlineStr"/>
-      <c r="P9" s="11" t="inlineStr"/>
+      <c r="P9" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
@@ -9749,7 +10285,11 @@
       <c r="U9" s="12" t="inlineStr"/>
       <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
-      <c r="X9" s="11" t="inlineStr"/>
+      <c r="X9" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y9" s="12" t="inlineStr"/>
       <c r="Z9" s="11" t="inlineStr"/>
       <c r="AA9" s="13" t="inlineStr"/>
@@ -9798,9 +10338,17 @@
         </is>
       </c>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="O10" s="12" t="inlineStr"/>
-      <c r="P10" s="11" t="inlineStr"/>
+      <c r="P10" s="11" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr">
         <is>
@@ -9809,14 +10357,18 @@
       </c>
       <c r="S10" s="12" t="inlineStr">
         <is>
-          <t>8I, D3</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="T10" s="11" t="inlineStr"/>
       <c r="U10" s="12" t="inlineStr"/>
       <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
-      <c r="X10" s="11" t="inlineStr"/>
+      <c r="X10" s="11" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="Y10" s="12" t="inlineStr"/>
       <c r="Z10" s="11" t="inlineStr"/>
       <c r="AA10" s="13" t="inlineStr"/>
@@ -9861,9 +10413,17 @@
       <c r="K11" s="12" t="inlineStr"/>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="O11" s="12" t="inlineStr"/>
-      <c r="P11" s="11" t="inlineStr"/>
+      <c r="P11" s="11" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
@@ -9871,7 +10431,11 @@
       <c r="U11" s="12" t="inlineStr"/>
       <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="12" t="inlineStr"/>
-      <c r="X11" s="11" t="inlineStr"/>
+      <c r="X11" s="11" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="Y11" s="12" t="inlineStr"/>
       <c r="Z11" s="11" t="inlineStr"/>
       <c r="AA11" s="13" t="inlineStr"/>
@@ -9924,9 +10488,21 @@
         </is>
       </c>
       <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="11" t="inlineStr"/>
-      <c r="O12" s="12" t="inlineStr"/>
-      <c r="P12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>8II, 2I</t>
+        </is>
+      </c>
+      <c r="P12" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr">
         <is>
@@ -9938,10 +10514,26 @@
           <t>3I, D4</t>
         </is>
       </c>
-      <c r="T12" s="11" t="inlineStr"/>
-      <c r="U12" s="12" t="inlineStr"/>
-      <c r="V12" s="11" t="inlineStr"/>
-      <c r="W12" s="12" t="inlineStr"/>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>2I, 2I</t>
+        </is>
+      </c>
+      <c r="U12" s="12" t="inlineStr">
+        <is>
+          <t>D1, A2, 8II</t>
+        </is>
+      </c>
+      <c r="V12" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="W12" s="12" t="inlineStr">
+        <is>
+          <t>1II/3II</t>
+        </is>
+      </c>
       <c r="X12" s="11" t="inlineStr"/>
       <c r="Y12" s="12" t="inlineStr"/>
       <c r="Z12" s="11" t="inlineStr"/>
@@ -9991,16 +10583,44 @@
       </c>
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr"/>
-      <c r="P13" s="11" t="inlineStr"/>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>8II, 2I</t>
+        </is>
+      </c>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
-      <c r="T13" s="11" t="inlineStr"/>
-      <c r="U13" s="12" t="inlineStr"/>
-      <c r="V13" s="11" t="inlineStr"/>
-      <c r="W13" s="12" t="inlineStr"/>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>2I, 2I</t>
+        </is>
+      </c>
+      <c r="U13" s="12" t="inlineStr">
+        <is>
+          <t>D1, A2, 8II</t>
+        </is>
+      </c>
+      <c r="V13" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="W13" s="12" t="inlineStr">
+        <is>
+          <t>1II/3II</t>
+        </is>
+      </c>
       <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
       <c r="Z13" s="11" t="inlineStr"/>
@@ -10062,9 +10682,17 @@
         </is>
       </c>
       <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="11" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>8II, 8I</t>
+        </is>
+      </c>
       <c r="O14" s="12" t="inlineStr"/>
-      <c r="P14" s="11" t="inlineStr"/>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr">
         <is>
@@ -10076,11 +10704,27 @@
           <t>1II/3II</t>
         </is>
       </c>
-      <c r="T14" s="11" t="inlineStr"/>
-      <c r="U14" s="12" t="inlineStr"/>
+      <c r="T14" s="11" t="inlineStr">
+        <is>
+          <t>2I, 4II, 8I</t>
+        </is>
+      </c>
+      <c r="U14" s="12" t="inlineStr">
+        <is>
+          <t>D1, D3</t>
+        </is>
+      </c>
       <c r="V14" s="11" t="inlineStr"/>
-      <c r="W14" s="12" t="inlineStr"/>
-      <c r="X14" s="11" t="inlineStr"/>
+      <c r="W14" s="12" t="inlineStr">
+        <is>
+          <t>3I, 1I</t>
+        </is>
+      </c>
+      <c r="X14" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y14" s="12" t="inlineStr"/>
       <c r="Z14" s="11" t="inlineStr"/>
       <c r="AA14" s="13" t="inlineStr"/>
@@ -10141,17 +10785,41 @@
         </is>
       </c>
       <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>8II, 8I</t>
+        </is>
+      </c>
       <c r="O15" s="12" t="inlineStr"/>
-      <c r="P15" s="11" t="inlineStr"/>
+      <c r="P15" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr"/>
-      <c r="U15" s="12" t="inlineStr"/>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>2I, 4II, 8I</t>
+        </is>
+      </c>
+      <c r="U15" s="12" t="inlineStr">
+        <is>
+          <t>D1, D3</t>
+        </is>
+      </c>
       <c r="V15" s="11" t="inlineStr"/>
-      <c r="W15" s="12" t="inlineStr"/>
-      <c r="X15" s="11" t="inlineStr"/>
+      <c r="W15" s="12" t="inlineStr">
+        <is>
+          <t>3I, 1I</t>
+        </is>
+      </c>
+      <c r="X15" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y15" s="12" t="inlineStr"/>
       <c r="Z15" s="11" t="inlineStr"/>
       <c r="AA15" s="13" t="inlineStr"/>
@@ -10216,7 +10884,11 @@
           <t>1II</t>
         </is>
       </c>
-      <c r="N16" s="11" t="inlineStr"/>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>8II, 8I</t>
+        </is>
+      </c>
       <c r="O16" s="12" t="inlineStr"/>
       <c r="P16" s="11" t="inlineStr"/>
       <c r="Q16" s="12" t="inlineStr"/>
@@ -10227,13 +10899,25 @@
       </c>
       <c r="S16" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 1I</t>
-        </is>
-      </c>
-      <c r="T16" s="11" t="inlineStr"/>
-      <c r="U16" s="12" t="inlineStr"/>
+          <t>1II/3II</t>
+        </is>
+      </c>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>2I, 4II, 8I</t>
+        </is>
+      </c>
+      <c r="U16" s="12" t="inlineStr">
+        <is>
+          <t>D1, D3</t>
+        </is>
+      </c>
       <c r="V16" s="11" t="inlineStr"/>
-      <c r="W16" s="12" t="inlineStr"/>
+      <c r="W16" s="12" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="X16" s="11" t="inlineStr"/>
       <c r="Y16" s="12" t="inlineStr"/>
       <c r="Z16" s="11" t="inlineStr"/>
@@ -10295,9 +10979,17 @@
           <t>3II, 3I</t>
         </is>
       </c>
-      <c r="N17" s="11" t="inlineStr"/>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>8II, 8I</t>
+        </is>
+      </c>
       <c r="O17" s="12" t="inlineStr"/>
-      <c r="P17" s="11" t="inlineStr"/>
+      <c r="P17" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr">
         <is>
@@ -10306,14 +10998,30 @@
       </c>
       <c r="S17" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 3I, D4</t>
-        </is>
-      </c>
-      <c r="T17" s="11" t="inlineStr"/>
-      <c r="U17" s="12" t="inlineStr"/>
+          <t>1II/3II, 3I</t>
+        </is>
+      </c>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>2I, 4II, 8I</t>
+        </is>
+      </c>
+      <c r="U17" s="12" t="inlineStr">
+        <is>
+          <t>D1, D3</t>
+        </is>
+      </c>
       <c r="V17" s="11" t="inlineStr"/>
-      <c r="W17" s="12" t="inlineStr"/>
-      <c r="X17" s="11" t="inlineStr"/>
+      <c r="W17" s="12" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="X17" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y17" s="12" t="inlineStr"/>
       <c r="Z17" s="11" t="inlineStr"/>
       <c r="AA17" s="13" t="inlineStr"/>
@@ -10374,17 +11082,41 @@
           <t>3II</t>
         </is>
       </c>
-      <c r="N18" s="11" t="inlineStr"/>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>8II, 8I</t>
+        </is>
+      </c>
       <c r="O18" s="12" t="inlineStr"/>
-      <c r="P18" s="11" t="inlineStr"/>
+      <c r="P18" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="11" t="inlineStr"/>
       <c r="S18" s="12" t="inlineStr"/>
-      <c r="T18" s="11" t="inlineStr"/>
-      <c r="U18" s="12" t="inlineStr"/>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>2I, 4II, 8I</t>
+        </is>
+      </c>
+      <c r="U18" s="12" t="inlineStr">
+        <is>
+          <t>D1, D3</t>
+        </is>
+      </c>
       <c r="V18" s="11" t="inlineStr"/>
-      <c r="W18" s="12" t="inlineStr"/>
-      <c r="X18" s="11" t="inlineStr"/>
+      <c r="W18" s="12" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="X18" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y18" s="12" t="inlineStr"/>
       <c r="Z18" s="11" t="inlineStr"/>
       <c r="AA18" s="13" t="inlineStr"/>
@@ -10445,9 +11177,21 @@
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="11" t="inlineStr"/>
-      <c r="O19" s="12" t="inlineStr"/>
-      <c r="P19" s="11" t="inlineStr"/>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O19" s="12" t="inlineStr">
+        <is>
+          <t>8II, 2I</t>
+        </is>
+      </c>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q19" s="12" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
@@ -10459,11 +11203,31 @@
           <t>1II/3II</t>
         </is>
       </c>
-      <c r="T19" s="11" t="inlineStr"/>
-      <c r="U19" s="12" t="inlineStr"/>
-      <c r="V19" s="11" t="inlineStr"/>
-      <c r="W19" s="12" t="inlineStr"/>
-      <c r="X19" s="11" t="inlineStr"/>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>2I, 2I</t>
+        </is>
+      </c>
+      <c r="U19" s="12" t="inlineStr">
+        <is>
+          <t>D1, A2, 6</t>
+        </is>
+      </c>
+      <c r="V19" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="W19" s="12" t="inlineStr">
+        <is>
+          <t>3I, 1I</t>
+        </is>
+      </c>
+      <c r="X19" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y19" s="12" t="inlineStr"/>
       <c r="Z19" s="11" t="inlineStr"/>
       <c r="AA19" s="13" t="inlineStr"/>
@@ -10524,17 +11288,49 @@
         </is>
       </c>
       <c r="M20" s="12" t="inlineStr"/>
-      <c r="N20" s="11" t="inlineStr"/>
-      <c r="O20" s="12" t="inlineStr"/>
-      <c r="P20" s="11" t="inlineStr"/>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t>8II, 2I</t>
+        </is>
+      </c>
+      <c r="P20" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q20" s="12" t="inlineStr"/>
       <c r="R20" s="11" t="inlineStr"/>
       <c r="S20" s="12" t="inlineStr"/>
-      <c r="T20" s="11" t="inlineStr"/>
-      <c r="U20" s="12" t="inlineStr"/>
-      <c r="V20" s="11" t="inlineStr"/>
-      <c r="W20" s="12" t="inlineStr"/>
-      <c r="X20" s="11" t="inlineStr"/>
+      <c r="T20" s="11" t="inlineStr">
+        <is>
+          <t>2I, 2I</t>
+        </is>
+      </c>
+      <c r="U20" s="12" t="inlineStr">
+        <is>
+          <t>D1, A2, 6</t>
+        </is>
+      </c>
+      <c r="V20" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="W20" s="12" t="inlineStr">
+        <is>
+          <t>3I, 1I</t>
+        </is>
+      </c>
+      <c r="X20" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y20" s="12" t="inlineStr"/>
       <c r="Z20" s="11" t="inlineStr"/>
       <c r="AA20" s="13" t="inlineStr"/>
@@ -10599,8 +11395,16 @@
           <t>1II</t>
         </is>
       </c>
-      <c r="N21" s="11" t="inlineStr"/>
-      <c r="O21" s="12" t="inlineStr"/>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O21" s="12" t="inlineStr">
+        <is>
+          <t>8II, 2I</t>
+        </is>
+      </c>
       <c r="P21" s="11" t="inlineStr"/>
       <c r="Q21" s="12" t="inlineStr"/>
       <c r="R21" s="11" t="inlineStr">
@@ -10610,13 +11414,29 @@
       </c>
       <c r="S21" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 1I</t>
-        </is>
-      </c>
-      <c r="T21" s="11" t="inlineStr"/>
-      <c r="U21" s="12" t="inlineStr"/>
-      <c r="V21" s="11" t="inlineStr"/>
-      <c r="W21" s="12" t="inlineStr"/>
+          <t>1II/3II</t>
+        </is>
+      </c>
+      <c r="T21" s="11" t="inlineStr">
+        <is>
+          <t>2I, 2I</t>
+        </is>
+      </c>
+      <c r="U21" s="12" t="inlineStr">
+        <is>
+          <t>D1, A2, 6</t>
+        </is>
+      </c>
+      <c r="V21" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="W21" s="12" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="X21" s="11" t="inlineStr"/>
       <c r="Y21" s="12" t="inlineStr"/>
       <c r="Z21" s="11" t="inlineStr"/>
@@ -10678,9 +11498,21 @@
           <t>3II, 3I</t>
         </is>
       </c>
-      <c r="N22" s="11" t="inlineStr"/>
-      <c r="O22" s="12" t="inlineStr"/>
-      <c r="P22" s="11" t="inlineStr"/>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t>8II, 2I</t>
+        </is>
+      </c>
+      <c r="P22" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q22" s="12" t="inlineStr"/>
       <c r="R22" s="11" t="inlineStr">
         <is>
@@ -10689,14 +11521,34 @@
       </c>
       <c r="S22" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 3I, D4</t>
-        </is>
-      </c>
-      <c r="T22" s="11" t="inlineStr"/>
-      <c r="U22" s="12" t="inlineStr"/>
-      <c r="V22" s="11" t="inlineStr"/>
-      <c r="W22" s="12" t="inlineStr"/>
-      <c r="X22" s="11" t="inlineStr"/>
+          <t>1II/3II, 3I</t>
+        </is>
+      </c>
+      <c r="T22" s="11" t="inlineStr">
+        <is>
+          <t>2I, 2I</t>
+        </is>
+      </c>
+      <c r="U22" s="12" t="inlineStr">
+        <is>
+          <t>D1, A2, 6</t>
+        </is>
+      </c>
+      <c r="V22" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="W22" s="12" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="X22" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y22" s="12" t="inlineStr"/>
       <c r="Z22" s="11" t="inlineStr"/>
       <c r="AA22" s="13" t="inlineStr"/>
@@ -10757,17 +11609,49 @@
           <t>3II</t>
         </is>
       </c>
-      <c r="N23" s="11" t="inlineStr"/>
-      <c r="O23" s="12" t="inlineStr"/>
-      <c r="P23" s="11" t="inlineStr"/>
+      <c r="N23" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O23" s="12" t="inlineStr">
+        <is>
+          <t>8II, 2I</t>
+        </is>
+      </c>
+      <c r="P23" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q23" s="12" t="inlineStr"/>
       <c r="R23" s="11" t="inlineStr"/>
       <c r="S23" s="12" t="inlineStr"/>
-      <c r="T23" s="11" t="inlineStr"/>
-      <c r="U23" s="12" t="inlineStr"/>
-      <c r="V23" s="11" t="inlineStr"/>
-      <c r="W23" s="12" t="inlineStr"/>
-      <c r="X23" s="11" t="inlineStr"/>
+      <c r="T23" s="11" t="inlineStr">
+        <is>
+          <t>2I, 2I</t>
+        </is>
+      </c>
+      <c r="U23" s="12" t="inlineStr">
+        <is>
+          <t>D1, A2, 6</t>
+        </is>
+      </c>
+      <c r="V23" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="W23" s="12" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="X23" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y23" s="12" t="inlineStr"/>
       <c r="Z23" s="11" t="inlineStr"/>
       <c r="AA23" s="13" t="inlineStr"/>
@@ -10810,15 +11694,19 @@
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr"/>
-      <c r="L24" s="11" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="L24" s="11" t="inlineStr"/>
       <c r="M24" s="12" t="inlineStr"/>
-      <c r="N24" s="11" t="inlineStr"/>
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="O24" s="12" t="inlineStr"/>
-      <c r="P24" s="11" t="inlineStr"/>
+      <c r="P24" s="11" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
       <c r="Q24" s="12" t="inlineStr"/>
       <c r="R24" s="11" t="inlineStr">
         <is>
@@ -10827,13 +11715,25 @@
       </c>
       <c r="S24" s="12" t="inlineStr">
         <is>
-          <t>1I, A1</t>
-        </is>
-      </c>
-      <c r="T24" s="11" t="inlineStr"/>
-      <c r="U24" s="12" t="inlineStr"/>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="T24" s="11" t="inlineStr">
+        <is>
+          <t>2I, 4II, 8II</t>
+        </is>
+      </c>
+      <c r="U24" s="12" t="inlineStr">
+        <is>
+          <t>D1, D3</t>
+        </is>
+      </c>
       <c r="V24" s="11" t="inlineStr"/>
-      <c r="W24" s="12" t="inlineStr"/>
+      <c r="W24" s="12" t="inlineStr">
+        <is>
+          <t>1II/3II</t>
+        </is>
+      </c>
       <c r="X24" s="11" t="inlineStr"/>
       <c r="Y24" s="12" t="inlineStr"/>
       <c r="Z24" s="11" t="inlineStr"/>
@@ -10879,16 +11779,36 @@
       <c r="K25" s="12" t="inlineStr"/>
       <c r="L25" s="11" t="inlineStr"/>
       <c r="M25" s="12" t="inlineStr"/>
-      <c r="N25" s="11" t="inlineStr"/>
+      <c r="N25" s="11" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="O25" s="12" t="inlineStr"/>
-      <c r="P25" s="11" t="inlineStr"/>
+      <c r="P25" s="11" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
       <c r="Q25" s="12" t="inlineStr"/>
       <c r="R25" s="11" t="inlineStr"/>
       <c r="S25" s="12" t="inlineStr"/>
-      <c r="T25" s="11" t="inlineStr"/>
-      <c r="U25" s="12" t="inlineStr"/>
+      <c r="T25" s="11" t="inlineStr">
+        <is>
+          <t>2I, 4II, 8II</t>
+        </is>
+      </c>
+      <c r="U25" s="12" t="inlineStr">
+        <is>
+          <t>D1, D3</t>
+        </is>
+      </c>
       <c r="V25" s="11" t="inlineStr"/>
-      <c r="W25" s="12" t="inlineStr"/>
+      <c r="W25" s="12" t="inlineStr">
+        <is>
+          <t>1II/3II</t>
+        </is>
+      </c>
       <c r="X25" s="11" t="inlineStr"/>
       <c r="Y25" s="12" t="inlineStr"/>
       <c r="Z25" s="11" t="inlineStr"/>
@@ -13621,7 +14541,11 @@
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
       <c r="N6" s="11" t="inlineStr"/>
-      <c r="O6" s="12" t="inlineStr"/>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr">
@@ -13630,8 +14554,16 @@
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr"/>
-      <c r="U6" s="12" t="inlineStr"/>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
+      <c r="U6" s="12" t="inlineStr">
+        <is>
+          <t>D3, A3</t>
+        </is>
+      </c>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
@@ -13692,13 +14624,25 @@
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr"/>
-      <c r="O7" s="12" t="inlineStr"/>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="P7" s="11" t="inlineStr"/>
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr"/>
-      <c r="U7" s="12" t="inlineStr"/>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
+      <c r="U7" s="12" t="inlineStr">
+        <is>
+          <t>D3, A3</t>
+        </is>
+      </c>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
@@ -13762,7 +14706,11 @@
       </c>
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>8I, 8II</t>
+        </is>
+      </c>
       <c r="O8" s="12" t="inlineStr"/>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
@@ -13772,8 +14720,16 @@
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr"/>
-      <c r="U8" s="12" t="inlineStr"/>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
+      <c r="U8" s="12" t="inlineStr">
+        <is>
+          <t>D3, A3</t>
+        </is>
+      </c>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
       <c r="X8" s="11" t="inlineStr"/>
@@ -13837,14 +14793,26 @@
       </c>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>8I, 8II</t>
+        </is>
+      </c>
       <c r="O9" s="12" t="inlineStr"/>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr"/>
-      <c r="U9" s="12" t="inlineStr"/>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
+      <c r="U9" s="12" t="inlineStr">
+        <is>
+          <t>D3, A3</t>
+        </is>
+      </c>
       <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
       <c r="X9" s="11" t="inlineStr"/>
@@ -13908,8 +14876,16 @@
       </c>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
-      <c r="O10" s="12" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>6, 4II</t>
+        </is>
+      </c>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr">
@@ -13918,9 +14894,17 @@
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr"/>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>4I, 2II, 4I</t>
+        </is>
+      </c>
       <c r="U10" s="12" t="inlineStr"/>
-      <c r="V10" s="11" t="inlineStr"/>
+      <c r="V10" s="11" t="inlineStr">
+        <is>
+          <t>4II, A2</t>
+        </is>
+      </c>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
       <c r="Y10" s="12" t="inlineStr"/>
@@ -13983,15 +14967,31 @@
       </c>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
-      <c r="O11" s="12" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>6, 4II</t>
+        </is>
+      </c>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr"/>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>4I, 2II, 4I</t>
+        </is>
+      </c>
       <c r="U11" s="12" t="inlineStr"/>
-      <c r="V11" s="11" t="inlineStr"/>
+      <c r="V11" s="11" t="inlineStr">
+        <is>
+          <t>4II, A2</t>
+        </is>
+      </c>
       <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="11" t="inlineStr"/>
       <c r="Y11" s="12" t="inlineStr"/>
@@ -14046,8 +15046,16 @@
       <c r="K12" s="12" t="inlineStr"/>
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="11" t="inlineStr"/>
-      <c r="O12" s="12" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>8II, 4II</t>
+        </is>
+      </c>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr">
@@ -14056,9 +15064,17 @@
         </is>
       </c>
       <c r="S12" s="12" t="inlineStr"/>
-      <c r="T12" s="11" t="inlineStr"/>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>4I, 2II, 4I</t>
+        </is>
+      </c>
       <c r="U12" s="12" t="inlineStr"/>
-      <c r="V12" s="11" t="inlineStr"/>
+      <c r="V12" s="11" t="inlineStr">
+        <is>
+          <t>4II, A2</t>
+        </is>
+      </c>
       <c r="W12" s="12" t="inlineStr"/>
       <c r="X12" s="11" t="inlineStr"/>
       <c r="Y12" s="12" t="inlineStr"/>
@@ -14113,15 +15129,31 @@
       <c r="K13" s="12" t="inlineStr"/>
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr"/>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>8II, 4II</t>
+        </is>
+      </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
-      <c r="T13" s="11" t="inlineStr"/>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>4I, 2II, 4I</t>
+        </is>
+      </c>
       <c r="U13" s="12" t="inlineStr"/>
-      <c r="V13" s="11" t="inlineStr"/>
+      <c r="V13" s="11" t="inlineStr">
+        <is>
+          <t>4II, A2</t>
+        </is>
+      </c>
       <c r="W13" s="12" t="inlineStr"/>
       <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
@@ -14190,7 +15222,11 @@
         </is>
       </c>
       <c r="S14" s="12" t="inlineStr"/>
-      <c r="T14" s="11" t="inlineStr"/>
+      <c r="T14" s="11" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="U14" s="12" t="inlineStr"/>
       <c r="V14" s="11" t="inlineStr"/>
       <c r="W14" s="12" t="inlineStr"/>
@@ -14257,7 +15293,11 @@
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr"/>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="U15" s="12" t="inlineStr"/>
       <c r="V15" s="11" t="inlineStr"/>
       <c r="W15" s="12" t="inlineStr"/>
@@ -14314,7 +15354,11 @@
       <c r="K16" s="12" t="inlineStr"/>
       <c r="L16" s="11" t="inlineStr"/>
       <c r="M16" s="12" t="inlineStr"/>
-      <c r="N16" s="11" t="inlineStr"/>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
       <c r="O16" s="12" t="inlineStr"/>
       <c r="P16" s="11" t="inlineStr"/>
       <c r="Q16" s="12" t="inlineStr"/>
@@ -14381,7 +15425,11 @@
       <c r="K17" s="12" t="inlineStr"/>
       <c r="L17" s="11" t="inlineStr"/>
       <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="11" t="inlineStr"/>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
       <c r="O17" s="12" t="inlineStr"/>
       <c r="P17" s="11" t="inlineStr"/>
       <c r="Q17" s="12" t="inlineStr"/>
@@ -17351,13 +18399,25 @@
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
       <c r="N6" s="11" t="inlineStr"/>
-      <c r="O6" s="12" t="inlineStr"/>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr"/>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr"/>
-      <c r="U6" s="12" t="inlineStr"/>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>4II, 2I</t>
+        </is>
+      </c>
+      <c r="U6" s="12" t="inlineStr">
+        <is>
+          <t>D3, D1</t>
+        </is>
+      </c>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
@@ -17413,14 +18473,26 @@
       </c>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>8I, 8II</t>
+        </is>
+      </c>
       <c r="O7" s="12" t="inlineStr"/>
       <c r="P7" s="11" t="inlineStr"/>
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr"/>
-      <c r="U7" s="12" t="inlineStr"/>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>4II, 2I</t>
+        </is>
+      </c>
+      <c r="U7" s="12" t="inlineStr">
+        <is>
+          <t>D3, D1</t>
+        </is>
+      </c>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
@@ -17476,15 +18548,35 @@
       </c>
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr"/>
-      <c r="O8" s="12" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>2I, 8II</t>
+        </is>
+      </c>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr"/>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr"/>
-      <c r="U8" s="12" t="inlineStr"/>
-      <c r="V8" s="11" t="inlineStr"/>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>2I, 2I</t>
+        </is>
+      </c>
+      <c r="U8" s="12" t="inlineStr">
+        <is>
+          <t>A2, D1</t>
+        </is>
+      </c>
+      <c r="V8" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="W8" s="12" t="inlineStr"/>
       <c r="X8" s="11" t="inlineStr"/>
       <c r="Y8" s="12" t="inlineStr"/>
@@ -17535,15 +18627,35 @@
       </c>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
-      <c r="O9" s="12" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>2I, 8II</t>
+        </is>
+      </c>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr"/>
-      <c r="U9" s="12" t="inlineStr"/>
-      <c r="V9" s="11" t="inlineStr"/>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>2I, 2I</t>
+        </is>
+      </c>
+      <c r="U9" s="12" t="inlineStr">
+        <is>
+          <t>A2, D1</t>
+        </is>
+      </c>
+      <c r="V9" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="W9" s="12" t="inlineStr"/>
       <c r="X9" s="11" t="inlineStr"/>
       <c r="Y9" s="12" t="inlineStr"/>
@@ -17590,7 +18702,11 @@
       <c r="K10" s="12" t="inlineStr"/>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
@@ -17645,7 +18761,11 @@
       </c>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -20792,16 +21912,28 @@
         </is>
       </c>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="O6" s="12" t="inlineStr"/>
-      <c r="P6" s="11" t="inlineStr"/>
+      <c r="P6" s="11" t="inlineStr">
+        <is>
+          <t>8I</t>
+        </is>
+      </c>
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr"/>
       <c r="S6" s="12" t="inlineStr"/>
       <c r="T6" s="11" t="inlineStr"/>
       <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
-      <c r="W6" s="12" t="inlineStr"/>
+      <c r="W6" s="12" t="inlineStr">
+        <is>
+          <t>8I</t>
+        </is>
+      </c>
       <c r="X6" s="11" t="inlineStr"/>
       <c r="Y6" s="12" t="inlineStr"/>
       <c r="Z6" s="11" t="inlineStr"/>
@@ -20855,9 +21987,17 @@
           <t>8II</t>
         </is>
       </c>
-      <c r="N7" s="11" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="O7" s="12" t="inlineStr"/>
-      <c r="P7" s="11" t="inlineStr"/>
+      <c r="P7" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
@@ -20865,7 +22005,11 @@
       <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
-      <c r="X7" s="11" t="inlineStr"/>
+      <c r="X7" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y7" s="12" t="inlineStr"/>
       <c r="Z7" s="11" t="inlineStr"/>
       <c r="AA7" s="13" t="inlineStr"/>
@@ -20910,7 +22054,11 @@
       <c r="K8" s="12" t="inlineStr"/>
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="O8" s="12" t="inlineStr"/>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
@@ -20965,7 +22113,11 @@
       <c r="K9" s="12" t="inlineStr"/>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="O9" s="12" t="inlineStr"/>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
@@ -21028,17 +22180,33 @@
         </is>
       </c>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="O10" s="12" t="inlineStr"/>
-      <c r="P10" s="11" t="inlineStr"/>
+      <c r="P10" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr"/>
       <c r="S10" s="12" t="inlineStr"/>
       <c r="T10" s="11" t="inlineStr"/>
       <c r="U10" s="12" t="inlineStr"/>
       <c r="V10" s="11" t="inlineStr"/>
-      <c r="W10" s="12" t="inlineStr"/>
-      <c r="X10" s="11" t="inlineStr"/>
+      <c r="W10" s="12" t="inlineStr">
+        <is>
+          <t>3I, 1I</t>
+        </is>
+      </c>
+      <c r="X10" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y10" s="12" t="inlineStr"/>
       <c r="Z10" s="11" t="inlineStr"/>
       <c r="AA10" s="13" t="inlineStr"/>
@@ -21091,17 +22259,33 @@
           <t>3II</t>
         </is>
       </c>
-      <c r="N11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="O11" s="12" t="inlineStr"/>
-      <c r="P11" s="11" t="inlineStr"/>
+      <c r="P11" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
       <c r="T11" s="11" t="inlineStr"/>
       <c r="U11" s="12" t="inlineStr"/>
       <c r="V11" s="11" t="inlineStr"/>
-      <c r="W11" s="12" t="inlineStr"/>
-      <c r="X11" s="11" t="inlineStr"/>
+      <c r="W11" s="12" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="X11" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y11" s="12" t="inlineStr"/>
       <c r="Z11" s="11" t="inlineStr"/>
       <c r="AA11" s="13" t="inlineStr"/>
@@ -21158,17 +22342,33 @@
         </is>
       </c>
       <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>8I</t>
+        </is>
+      </c>
       <c r="O12" s="12" t="inlineStr"/>
-      <c r="P12" s="11" t="inlineStr"/>
+      <c r="P12" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr"/>
       <c r="S12" s="12" t="inlineStr"/>
       <c r="T12" s="11" t="inlineStr"/>
       <c r="U12" s="12" t="inlineStr"/>
       <c r="V12" s="11" t="inlineStr"/>
-      <c r="W12" s="12" t="inlineStr"/>
-      <c r="X12" s="11" t="inlineStr"/>
+      <c r="W12" s="12" t="inlineStr">
+        <is>
+          <t>3I, 1I</t>
+        </is>
+      </c>
+      <c r="X12" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y12" s="12" t="inlineStr"/>
       <c r="Z12" s="11" t="inlineStr"/>
       <c r="AA12" s="13" t="inlineStr"/>
@@ -21225,17 +22425,33 @@
           <t>3II</t>
         </is>
       </c>
-      <c r="N13" s="11" t="inlineStr"/>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>8I</t>
+        </is>
+      </c>
       <c r="O13" s="12" t="inlineStr"/>
-      <c r="P13" s="11" t="inlineStr"/>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
       <c r="T13" s="11" t="inlineStr"/>
       <c r="U13" s="12" t="inlineStr"/>
       <c r="V13" s="11" t="inlineStr"/>
-      <c r="W13" s="12" t="inlineStr"/>
-      <c r="X13" s="11" t="inlineStr"/>
+      <c r="W13" s="12" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="X13" s="11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
       <c r="Y13" s="12" t="inlineStr"/>
       <c r="Z13" s="11" t="inlineStr"/>
       <c r="AA13" s="13" t="inlineStr"/>
@@ -21281,7 +22497,11 @@
       <c r="L14" s="11" t="inlineStr"/>
       <c r="M14" s="12" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr"/>
-      <c r="O14" s="12" t="inlineStr"/>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr"/>
@@ -21339,13 +22559,21 @@
       </c>
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="O15" s="12" t="inlineStr"/>
       <c r="P15" s="11" t="inlineStr"/>
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr"/>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>4I</t>
+        </is>
+      </c>
       <c r="U15" s="12" t="inlineStr"/>
       <c r="V15" s="11" t="inlineStr"/>
       <c r="W15" s="12" t="inlineStr"/>
@@ -21394,13 +22622,21 @@
       <c r="K16" s="12" t="inlineStr"/>
       <c r="L16" s="11" t="inlineStr"/>
       <c r="M16" s="12" t="inlineStr"/>
-      <c r="N16" s="11" t="inlineStr"/>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="O16" s="12" t="inlineStr"/>
       <c r="P16" s="11" t="inlineStr"/>
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr"/>
       <c r="S16" s="12" t="inlineStr"/>
-      <c r="T16" s="11" t="inlineStr"/>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>4I</t>
+        </is>
+      </c>
       <c r="U16" s="12" t="inlineStr"/>
       <c r="V16" s="11" t="inlineStr"/>
       <c r="W16" s="12" t="inlineStr"/>
@@ -21458,16 +22694,40 @@
       </c>
       <c r="M17" s="12" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr"/>
-      <c r="O17" s="12" t="inlineStr"/>
-      <c r="P17" s="11" t="inlineStr"/>
+      <c r="O17" s="12" t="inlineStr">
+        <is>
+          <t>8II, 2I</t>
+        </is>
+      </c>
+      <c r="P17" s="11" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr"/>
       <c r="S17" s="12" t="inlineStr"/>
-      <c r="T17" s="11" t="inlineStr"/>
-      <c r="U17" s="12" t="inlineStr"/>
-      <c r="V17" s="11" t="inlineStr"/>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
+      <c r="U17" s="12" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="V17" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="W17" s="12" t="inlineStr"/>
-      <c r="X17" s="11" t="inlineStr"/>
+      <c r="X17" s="11" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="Y17" s="12" t="inlineStr"/>
       <c r="Z17" s="11" t="inlineStr"/>
       <c r="AA17" s="13" t="inlineStr"/>
@@ -21521,14 +22781,30 @@
         </is>
       </c>
       <c r="N18" s="11" t="inlineStr"/>
-      <c r="O18" s="12" t="inlineStr"/>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>8II, 2I</t>
+        </is>
+      </c>
       <c r="P18" s="11" t="inlineStr"/>
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="11" t="inlineStr"/>
       <c r="S18" s="12" t="inlineStr"/>
-      <c r="T18" s="11" t="inlineStr"/>
-      <c r="U18" s="12" t="inlineStr"/>
-      <c r="V18" s="11" t="inlineStr"/>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>2I</t>
+        </is>
+      </c>
+      <c r="U18" s="12" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="V18" s="11" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
       <c r="W18" s="12" t="inlineStr"/>
       <c r="X18" s="11" t="inlineStr"/>
       <c r="Y18" s="12" t="inlineStr"/>
@@ -21583,16 +22859,32 @@
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="11" t="inlineStr"/>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="O19" s="12" t="inlineStr"/>
       <c r="P19" s="11" t="inlineStr"/>
       <c r="Q19" s="12" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr"/>
       <c r="S19" s="12" t="inlineStr"/>
-      <c r="T19" s="11" t="inlineStr"/>
-      <c r="U19" s="12" t="inlineStr"/>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
+      <c r="U19" s="12" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="V19" s="11" t="inlineStr"/>
-      <c r="W19" s="12" t="inlineStr"/>
+      <c r="W19" s="12" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="X19" s="11" t="inlineStr"/>
       <c r="Y19" s="12" t="inlineStr"/>
       <c r="Z19" s="11" t="inlineStr"/>
@@ -21646,14 +22938,26 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N20" s="11" t="inlineStr"/>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="O20" s="12" t="inlineStr"/>
       <c r="P20" s="11" t="inlineStr"/>
       <c r="Q20" s="12" t="inlineStr"/>
       <c r="R20" s="11" t="inlineStr"/>
       <c r="S20" s="12" t="inlineStr"/>
-      <c r="T20" s="11" t="inlineStr"/>
-      <c r="U20" s="12" t="inlineStr"/>
+      <c r="T20" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
+      <c r="U20" s="12" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
       <c r="V20" s="11" t="inlineStr"/>
       <c r="W20" s="12" t="inlineStr"/>
       <c r="X20" s="11" t="inlineStr"/>
@@ -25015,7 +26319,7 @@
       </c>
       <c r="C8" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">main_ol_distance 150
+          <t xml:space="preserve">main_ol_distance 120
 </t>
         </is>
       </c>
@@ -25204,191 +26508,191 @@
       </c>
       <c r="C17" s="41" t="inlineStr">
         <is>
+          <t xml:space="preserve">OL_delay_dist_weight 0.18
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NDE C A1
+</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2II 21693 21629 21579
+</t>
+        </is>
+      </c>
+      <c r="C18" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OL_delay_dist_bias 15
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEC 1II/3II
+</t>
+        </is>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2I 21693 21579 21629
+</t>
+        </is>
+      </c>
+      <c r="C19" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARC_delay_dist_weight 0.08
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NDE A III
+</t>
+        </is>
+      </c>
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    A3 21850 21693
+</t>
+        </is>
+      </c>
+      <c r="C20" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERC_delay_circ_multiplier 0.12
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        SWP S6/M6
+</t>
+        </is>
+      </c>
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    D1 21850 21693
+</t>
+        </is>
+      </c>
+      <c r="C21" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERC_delay_shunt_multiplier 0.36
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NDE B 3I
+</t>
+        </is>
+      </c>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SWIS
+</t>
+        </is>
+      </c>
+      <c r="C22" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC_min_delay 60
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        SWI 3II
+</t>
+        </is>
+      </c>
+      <c r="B23" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    1I 20747 20816
+</t>
+        </is>
+      </c>
+      <c r="C23" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC_max_delay 255
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NDE C
+</t>
+        </is>
+      </c>
+      <c r="B24" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    1II 20835 20755
+</t>
+        </is>
+      </c>
+      <c r="C24" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delay_round_multiple 5
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NDE D 1I
+</t>
+        </is>
+      </c>
+      <c r="B25" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2I 21673 21585
+</t>
+        </is>
+      </c>
+      <c r="C25" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delay_round_down_allowed False
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        SWI 1II
+</t>
+        </is>
+      </c>
+      <c r="B26" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2II 21585 21673
+</t>
+        </is>
+      </c>
+      <c r="C26" s="41" t="inlineStr">
+        <is>
           <t xml:space="preserve">shunt_sig_filters_fp True
 </t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NDE C A1
-</t>
-        </is>
-      </c>
-      <c r="B18" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    2II 21693 21629 21579
-</t>
-        </is>
-      </c>
-      <c r="C18" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OL_delay_dist_weight 0.18
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEC 1II/3II
-</t>
-        </is>
-      </c>
-      <c r="B19" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    2I 21693 21579 21629
-</t>
-        </is>
-      </c>
-      <c r="C19" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OL_delay_dist_bias 15
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NDE A III
-</t>
-        </is>
-      </c>
-      <c r="B20" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    A3 21850 21693
-</t>
-        </is>
-      </c>
-      <c r="C20" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ARC_delay_dist_weight 0.08
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        SWP S6/M6
-</t>
-        </is>
-      </c>
-      <c r="B21" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    D1 21850 21693
-</t>
-        </is>
-      </c>
-      <c r="C21" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ERC_delay_circ_multiplier 0.12
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NDE B 3I
-</t>
-        </is>
-      </c>
-      <c r="B22" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SWIS
-</t>
-        </is>
-      </c>
-      <c r="C22" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ERC_delay_shunt_multiplier 0.36
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        SWI 3II
-</t>
-        </is>
-      </c>
-      <c r="B23" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    1I 20747 20816
-</t>
-        </is>
-      </c>
-      <c r="C23" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RC_min_delay 60
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NDE C
-</t>
-        </is>
-      </c>
-      <c r="B24" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    1II 20835 20755
-</t>
-        </is>
-      </c>
-      <c r="C24" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RC_max_delay 255
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NDE D 1I
-</t>
-        </is>
-      </c>
-      <c r="B25" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    2I 21673 21585
-</t>
-        </is>
-      </c>
-      <c r="C25" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delay_round_multiple 5
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        SWI 1II
-</t>
-        </is>
-      </c>
-      <c r="B26" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    2II 21585 21673
-</t>
-        </is>
-      </c>
-      <c r="C26" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delay_round_down_allowed False
-</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
       <c r="A27" s="38" t="inlineStr">
         <is>
@@ -25402,7 +26706,12 @@
 </t>
         </is>
       </c>
-      <c r="C27" s="41" t="n"/>
+      <c r="C27" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vital_fp_threshold 6
+</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="38" t="inlineStr">
@@ -25417,7 +26726,12 @@
 </t>
         </is>
       </c>
-      <c r="C28" s="41" t="n"/>
+      <c r="C28" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sub_vital_fp_threshold 50
+</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="38" t="inlineStr">
@@ -25432,7 +26746,12 @@
 </t>
         </is>
       </c>
-      <c r="C29" s="41" t="n"/>
+      <c r="C29" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">remote_fp_threshold 150
+</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="38" t="inlineStr">

--- a/stations/output/SPE_Interlocking_Program.xlsx
+++ b/stations/output/SPE_Interlocking_Program.xlsx
@@ -1206,7 +1206,7 @@
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v0.24.1</t>
+          <t>v1.0.0</t>
         </is>
       </c>
     </row>
@@ -1757,17 +1757,13 @@
       </c>
       <c r="S6" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6, A2</t>
         </is>
       </c>
       <c r="T6" s="11" t="inlineStr"/>
       <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
-      <c r="W6" s="12" t="inlineStr">
-        <is>
-          <t>8II</t>
-        </is>
-      </c>
+      <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
       <c r="Y6" s="12" t="inlineStr"/>
       <c r="Z6" s="11" t="inlineStr"/>
@@ -1830,11 +1826,7 @@
       <c r="T7" s="11" t="inlineStr"/>
       <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
-      <c r="W7" s="12" t="inlineStr">
-        <is>
-          <t>8II</t>
-        </is>
-      </c>
+      <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
       <c r="Y7" s="12" t="inlineStr"/>
       <c r="Z7" s="11" t="inlineStr"/>
@@ -1891,8 +1883,16 @@
           <t>8II</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr"/>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="O8" s="12" t="inlineStr"/>
       <c r="P8" s="11" t="inlineStr">
         <is>
@@ -1910,11 +1910,7 @@
           <t>8II, 6</t>
         </is>
       </c>
-      <c r="T8" s="11" t="inlineStr">
-        <is>
-          <t>3I</t>
-        </is>
-      </c>
+      <c r="T8" s="11" t="inlineStr"/>
       <c r="U8" s="12" t="inlineStr"/>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
@@ -1949,12 +1945,12 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>8II+</t>
+          <t>8II-</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr"/>
@@ -1969,27 +1965,35 @@
           <t>1I, 1II</t>
         </is>
       </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>8II</t>
-        </is>
-      </c>
-      <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
+      <c r="L9" s="11" t="inlineStr"/>
+      <c r="M9" s="12" t="inlineStr">
+        <is>
+          <t>8II, 8I</t>
+        </is>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="O9" s="12" t="inlineStr"/>
       <c r="P9" s="11" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr"/>
-      <c r="R9" s="11" t="inlineStr"/>
-      <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr">
-        <is>
-          <t>3I</t>
-        </is>
-      </c>
+      <c r="R9" s="11" t="inlineStr">
+        <is>
+          <t>A1, 1I, 1II/3II, III</t>
+        </is>
+      </c>
+      <c r="S9" s="12" t="inlineStr">
+        <is>
+          <t>8II, 8I</t>
+        </is>
+      </c>
+      <c r="T9" s="11" t="inlineStr"/>
       <c r="U9" s="12" t="inlineStr"/>
       <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
@@ -2024,12 +2028,12 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>8II-</t>
+          <t>8II+</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr"/>
@@ -2044,35 +2048,27 @@
           <t>1I, 1II</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr"/>
-      <c r="M10" s="12" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>8II</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr"/>
+      <c r="M10" s="12" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr"/>
-      <c r="R10" s="11" t="inlineStr">
-        <is>
-          <t>A1, 1I, 1II/3II, III</t>
-        </is>
-      </c>
-      <c r="S10" s="12" t="inlineStr">
-        <is>
-          <t>8II, 8I</t>
-        </is>
-      </c>
-      <c r="T10" s="11" t="inlineStr">
-        <is>
-          <t>3I</t>
-        </is>
-      </c>
+      <c r="R10" s="11" t="inlineStr"/>
+      <c r="S10" s="12" t="inlineStr"/>
+      <c r="T10" s="11" t="inlineStr"/>
       <c r="U10" s="12" t="inlineStr"/>
       <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
@@ -2133,7 +2129,11 @@
           <t>8II</t>
         </is>
       </c>
-      <c r="N11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr">
         <is>
@@ -2143,11 +2143,7 @@
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr">
-        <is>
-          <t>3I</t>
-        </is>
-      </c>
+      <c r="T11" s="11" t="inlineStr"/>
       <c r="U11" s="12" t="inlineStr"/>
       <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="12" t="inlineStr"/>
@@ -2202,7 +2198,7 @@
       <c r="M12" s="12" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>4II, 8II</t>
+          <t>2II, 4I</t>
         </is>
       </c>
       <c r="O12" s="12" t="inlineStr"/>
@@ -2222,22 +2218,14 @@
           <t>3I, D4</t>
         </is>
       </c>
-      <c r="T12" s="11" t="inlineStr">
-        <is>
-          <t>2II, 4I, 4I</t>
-        </is>
-      </c>
+      <c r="T12" s="11" t="inlineStr"/>
       <c r="U12" s="12" t="inlineStr">
         <is>
           <t>8II</t>
         </is>
       </c>
       <c r="V12" s="11" t="inlineStr"/>
-      <c r="W12" s="12" t="inlineStr">
-        <is>
-          <t>1II/3II</t>
-        </is>
-      </c>
+      <c r="W12" s="12" t="inlineStr"/>
       <c r="X12" s="11" t="inlineStr"/>
       <c r="Y12" s="12" t="inlineStr"/>
       <c r="Z12" s="11" t="inlineStr"/>
@@ -2285,7 +2273,7 @@
       <c r="M13" s="12" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>4II, 8II</t>
+          <t>2II, 4I</t>
         </is>
       </c>
       <c r="O13" s="12" t="inlineStr"/>
@@ -2297,22 +2285,14 @@
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
-      <c r="T13" s="11" t="inlineStr">
-        <is>
-          <t>2II, 4I, 4I</t>
-        </is>
-      </c>
+      <c r="T13" s="11" t="inlineStr"/>
       <c r="U13" s="12" t="inlineStr">
         <is>
           <t>8II</t>
         </is>
       </c>
       <c r="V13" s="11" t="inlineStr"/>
-      <c r="W13" s="12" t="inlineStr">
-        <is>
-          <t>1II/3II</t>
-        </is>
-      </c>
+      <c r="W13" s="12" t="inlineStr"/>
       <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
       <c r="Z13" s="11" t="inlineStr"/>
@@ -2376,13 +2356,13 @@
       <c r="M14" s="12" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>4II, 6</t>
+          <t>2II, 4I, 6</t>
         </is>
       </c>
       <c r="O14" s="12" t="inlineStr"/>
       <c r="P14" s="11" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>3I, 1I</t>
         </is>
       </c>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -2396,27 +2376,11 @@
           <t>1II/3II</t>
         </is>
       </c>
-      <c r="T14" s="11" t="inlineStr">
-        <is>
-          <t>2II, 4I, 4I</t>
-        </is>
-      </c>
-      <c r="U14" s="12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="T14" s="11" t="inlineStr"/>
+      <c r="U14" s="12" t="inlineStr"/>
       <c r="V14" s="11" t="inlineStr"/>
-      <c r="W14" s="12" t="inlineStr">
-        <is>
-          <t>3I, 1I</t>
-        </is>
-      </c>
-      <c r="X14" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+      <c r="W14" s="12" t="inlineStr"/>
+      <c r="X14" s="11" t="inlineStr"/>
       <c r="Y14" s="12" t="inlineStr"/>
       <c r="Z14" s="11" t="inlineStr"/>
       <c r="AA14" s="13" t="inlineStr"/>
@@ -2447,12 +2411,12 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>3II+</t>
+          <t>3II+/1II-</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -2476,42 +2440,38 @@
           <t>3II</t>
         </is>
       </c>
-      <c r="M15" s="12" t="inlineStr"/>
+      <c r="M15" s="12" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>4II, 6</t>
+          <t>2II, 4I, 6</t>
         </is>
       </c>
       <c r="O15" s="12" t="inlineStr"/>
       <c r="P15" s="11" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>3I</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr"/>
-      <c r="R15" s="11" t="inlineStr"/>
-      <c r="S15" s="12" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr">
-        <is>
-          <t>2II, 4I, 4I</t>
-        </is>
-      </c>
-      <c r="U15" s="12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="R15" s="11" t="inlineStr">
+        <is>
+          <t>D1, 2I, 4II, D3, 8I, 8II, III</t>
+        </is>
+      </c>
+      <c r="S15" s="12" t="inlineStr">
+        <is>
+          <t>1II/3II, 1I</t>
+        </is>
+      </c>
+      <c r="T15" s="11" t="inlineStr"/>
+      <c r="U15" s="12" t="inlineStr"/>
       <c r="V15" s="11" t="inlineStr"/>
-      <c r="W15" s="12" t="inlineStr">
-        <is>
-          <t>3I, 1I</t>
-        </is>
-      </c>
-      <c r="X15" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+      <c r="W15" s="12" t="inlineStr"/>
+      <c r="X15" s="11" t="inlineStr"/>
       <c r="Y15" s="12" t="inlineStr"/>
       <c r="Z15" s="11" t="inlineStr"/>
       <c r="AA15" s="13" t="inlineStr"/>
@@ -2547,7 +2507,7 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>3II+/1II-</t>
+          <t>3II-</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -2566,23 +2526,23 @@
           <t>8I, 8II</t>
         </is>
       </c>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>3II</t>
-        </is>
-      </c>
+      <c r="L16" s="11" t="inlineStr"/>
       <c r="M16" s="12" t="inlineStr">
         <is>
-          <t>1II</t>
+          <t>3II, 3I</t>
         </is>
       </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>4II, 6</t>
+          <t>2II, 4I, 6</t>
         </is>
       </c>
       <c r="O16" s="12" t="inlineStr"/>
-      <c r="P16" s="11" t="inlineStr"/>
+      <c r="P16" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr">
         <is>
@@ -2591,25 +2551,13 @@
       </c>
       <c r="S16" s="12" t="inlineStr">
         <is>
-          <t>1II/3II</t>
-        </is>
-      </c>
-      <c r="T16" s="11" t="inlineStr">
-        <is>
-          <t>2II, 4I, 4I</t>
-        </is>
-      </c>
-      <c r="U16" s="12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>1II/3II, 3I, D4</t>
+        </is>
+      </c>
+      <c r="T16" s="11" t="inlineStr"/>
+      <c r="U16" s="12" t="inlineStr"/>
       <c r="V16" s="11" t="inlineStr"/>
-      <c r="W16" s="12" t="inlineStr">
-        <is>
-          <t>3I</t>
-        </is>
-      </c>
+      <c r="W16" s="12" t="inlineStr"/>
       <c r="X16" s="11" t="inlineStr"/>
       <c r="Y16" s="12" t="inlineStr"/>
       <c r="Z16" s="11" t="inlineStr"/>
@@ -2646,74 +2594,62 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>3II-</t>
+          <t>3II+/1II+</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>2I+</t>
+          <t>2I-</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>2I, 4II</t>
+          <t>4I, 8II</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>8I, 8II</t>
-        </is>
-      </c>
-      <c r="L17" s="11" t="inlineStr"/>
-      <c r="M17" s="12" t="inlineStr">
-        <is>
-          <t>3II, 3I</t>
-        </is>
-      </c>
+          <t>2I, 2II, 6</t>
+        </is>
+      </c>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
+          <t>3II, 1II</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>4II, 6</t>
+          <t>4II, 8I</t>
         </is>
       </c>
       <c r="O17" s="12" t="inlineStr"/>
       <c r="P17" s="11" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>3I, 1I</t>
         </is>
       </c>
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>D1, 2I, 4II, D3, 8I, 8II, III</t>
+          <t>D1, 2I, 2II, 4I, A2, 6, 8II, III</t>
         </is>
       </c>
       <c r="S17" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 3I</t>
-        </is>
-      </c>
-      <c r="T17" s="11" t="inlineStr">
-        <is>
-          <t>2II, 4I, 4I</t>
-        </is>
-      </c>
+          <t>1II/3II</t>
+        </is>
+      </c>
+      <c r="T17" s="11" t="inlineStr"/>
       <c r="U17" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="V17" s="11" t="inlineStr"/>
-      <c r="W17" s="12" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
-      <c r="X17" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+      <c r="W17" s="12" t="inlineStr"/>
+      <c r="X17" s="11" t="inlineStr"/>
       <c r="Y17" s="12" t="inlineStr"/>
       <c r="Z17" s="11" t="inlineStr"/>
       <c r="AA17" s="13" t="inlineStr"/>
@@ -2744,71 +2680,71 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>3II-</t>
+          <t>3II+/1II-</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>2I+</t>
+          <t>2I-</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr"/>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>2I, 4II</t>
+          <t>4I, 8II</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>8I, 8II</t>
-        </is>
-      </c>
-      <c r="L18" s="11" t="inlineStr"/>
+          <t>2I, 2II, 6</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="M18" s="12" t="inlineStr">
         <is>
-          <t>3II</t>
+          <t>1II</t>
         </is>
       </c>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>4II, 6</t>
+          <t>4II, 8I</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr"/>
       <c r="P18" s="11" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>3I</t>
         </is>
       </c>
       <c r="Q18" s="12" t="inlineStr"/>
-      <c r="R18" s="11" t="inlineStr"/>
-      <c r="S18" s="12" t="inlineStr"/>
-      <c r="T18" s="11" t="inlineStr">
-        <is>
-          <t>2II, 4I, 4I</t>
-        </is>
-      </c>
+      <c r="R18" s="11" t="inlineStr">
+        <is>
+          <t>D1, 2I, 2II, 4I, A2, 6, 8II, III</t>
+        </is>
+      </c>
+      <c r="S18" s="12" t="inlineStr">
+        <is>
+          <t>1II/3II, 1I</t>
+        </is>
+      </c>
+      <c r="T18" s="11" t="inlineStr"/>
       <c r="U18" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="V18" s="11" t="inlineStr"/>
-      <c r="W18" s="12" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
-      <c r="X18" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+      <c r="W18" s="12" t="inlineStr"/>
+      <c r="X18" s="11" t="inlineStr"/>
       <c r="Y18" s="12" t="inlineStr"/>
       <c r="Z18" s="11" t="inlineStr"/>
       <c r="AA18" s="13" t="inlineStr"/>
@@ -2844,7 +2780,7 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>3II+/1II+</t>
+          <t>3II-</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -2863,15 +2799,15 @@
           <t>2I, 2II, 6</t>
         </is>
       </c>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>3II, 1II</t>
-        </is>
-      </c>
-      <c r="M19" s="12" t="inlineStr"/>
+      <c r="L19" s="11" t="inlineStr"/>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>3II, 3I</t>
+        </is>
+      </c>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>8II, 8I</t>
+          <t>4II, 8I</t>
         </is>
       </c>
       <c r="O19" s="12" t="inlineStr"/>
@@ -2888,30 +2824,18 @@
       </c>
       <c r="S19" s="12" t="inlineStr">
         <is>
-          <t>1II/3II</t>
-        </is>
-      </c>
-      <c r="T19" s="11" t="inlineStr">
-        <is>
-          <t>4II, 8I</t>
-        </is>
-      </c>
+          <t>1II/3II, 3I, D4</t>
+        </is>
+      </c>
+      <c r="T19" s="11" t="inlineStr"/>
       <c r="U19" s="12" t="inlineStr">
         <is>
-          <t>A3, D3</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="V19" s="11" t="inlineStr"/>
-      <c r="W19" s="12" t="inlineStr">
-        <is>
-          <t>3I, 1I</t>
-        </is>
-      </c>
-      <c r="X19" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+      <c r="W19" s="12" t="inlineStr"/>
+      <c r="X19" s="11" t="inlineStr"/>
       <c r="Y19" s="12" t="inlineStr"/>
       <c r="Z19" s="11" t="inlineStr"/>
       <c r="AA19" s="13" t="inlineStr"/>
@@ -2952,18 +2876,18 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>2I-</t>
+          <t>2I+</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr"/>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>4I, 8II</t>
+          <t>2I, 4II</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>2I, 2II, 6</t>
+          <t>8I, 8II</t>
         </is>
       </c>
       <c r="L20" s="11" t="inlineStr">
@@ -2974,39 +2898,23 @@
       <c r="M20" s="12" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>8II, 8I</t>
+          <t>2II, 4I, 6</t>
         </is>
       </c>
       <c r="O20" s="12" t="inlineStr"/>
       <c r="P20" s="11" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>3I, 1I</t>
         </is>
       </c>
       <c r="Q20" s="12" t="inlineStr"/>
       <c r="R20" s="11" t="inlineStr"/>
       <c r="S20" s="12" t="inlineStr"/>
-      <c r="T20" s="11" t="inlineStr">
-        <is>
-          <t>4II, 8I</t>
-        </is>
-      </c>
-      <c r="U20" s="12" t="inlineStr">
-        <is>
-          <t>A3, D3</t>
-        </is>
-      </c>
+      <c r="T20" s="11" t="inlineStr"/>
+      <c r="U20" s="12" t="inlineStr"/>
       <c r="V20" s="11" t="inlineStr"/>
-      <c r="W20" s="12" t="inlineStr">
-        <is>
-          <t>3I, 1I</t>
-        </is>
-      </c>
-      <c r="X20" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+      <c r="W20" s="12" t="inlineStr"/>
+      <c r="X20" s="11" t="inlineStr"/>
       <c r="Y20" s="12" t="inlineStr"/>
       <c r="Z20" s="11" t="inlineStr"/>
       <c r="AA20" s="13" t="inlineStr"/>
@@ -3037,74 +2945,54 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>3II+/1II-</t>
+          <t>3II-</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>2I-</t>
+          <t>2I+</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr"/>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>4I, 8II</t>
+          <t>2I, 4II</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>2I, 2II, 6</t>
-        </is>
-      </c>
-      <c r="L21" s="11" t="inlineStr">
+          <t>8I, 8II</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr"/>
+      <c r="M21" s="12" t="inlineStr">
         <is>
           <t>3II</t>
         </is>
       </c>
-      <c r="M21" s="12" t="inlineStr">
-        <is>
-          <t>1II</t>
-        </is>
-      </c>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>8II, 8I</t>
+          <t>2II, 4I, 6</t>
         </is>
       </c>
       <c r="O21" s="12" t="inlineStr"/>
-      <c r="P21" s="11" t="inlineStr"/>
+      <c r="P21" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q21" s="12" t="inlineStr"/>
-      <c r="R21" s="11" t="inlineStr">
-        <is>
-          <t>D1, 2I, 2II, 4I, A2, 6, 8II, III</t>
-        </is>
-      </c>
-      <c r="S21" s="12" t="inlineStr">
-        <is>
-          <t>1II/3II</t>
-        </is>
-      </c>
-      <c r="T21" s="11" t="inlineStr">
-        <is>
-          <t>4II, 8I</t>
-        </is>
-      </c>
-      <c r="U21" s="12" t="inlineStr">
-        <is>
-          <t>A3, D3</t>
-        </is>
-      </c>
+      <c r="R21" s="11" t="inlineStr"/>
+      <c r="S21" s="12" t="inlineStr"/>
+      <c r="T21" s="11" t="inlineStr"/>
+      <c r="U21" s="12" t="inlineStr"/>
       <c r="V21" s="11" t="inlineStr"/>
-      <c r="W21" s="12" t="inlineStr">
-        <is>
-          <t>3I</t>
-        </is>
-      </c>
+      <c r="W21" s="12" t="inlineStr"/>
       <c r="X21" s="11" t="inlineStr"/>
       <c r="Y21" s="12" t="inlineStr"/>
       <c r="Z21" s="11" t="inlineStr"/>
@@ -3136,12 +3024,12 @@
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>3II-</t>
+          <t>3II+</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -3160,55 +3048,35 @@
           <t>2I, 2II, 6</t>
         </is>
       </c>
-      <c r="L22" s="11" t="inlineStr"/>
-      <c r="M22" s="12" t="inlineStr">
-        <is>
-          <t>3II, 3I</t>
-        </is>
-      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="M22" s="12" t="inlineStr"/>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>8II, 8I</t>
+          <t>4II, 8I</t>
         </is>
       </c>
       <c r="O22" s="12" t="inlineStr"/>
       <c r="P22" s="11" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>3I, 1I</t>
         </is>
       </c>
       <c r="Q22" s="12" t="inlineStr"/>
-      <c r="R22" s="11" t="inlineStr">
-        <is>
-          <t>D1, 2I, 2II, 4I, A2, 6, 8II, III</t>
-        </is>
-      </c>
-      <c r="S22" s="12" t="inlineStr">
-        <is>
-          <t>1II/3II, 3I</t>
-        </is>
-      </c>
-      <c r="T22" s="11" t="inlineStr">
-        <is>
-          <t>4II, 8I</t>
-        </is>
-      </c>
+      <c r="R22" s="11" t="inlineStr"/>
+      <c r="S22" s="12" t="inlineStr"/>
+      <c r="T22" s="11" t="inlineStr"/>
       <c r="U22" s="12" t="inlineStr">
         <is>
-          <t>A3, D3</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="V22" s="11" t="inlineStr"/>
-      <c r="W22" s="12" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
-      <c r="X22" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+      <c r="W22" s="12" t="inlineStr"/>
+      <c r="X22" s="11" t="inlineStr"/>
       <c r="Y22" s="12" t="inlineStr"/>
       <c r="Z22" s="11" t="inlineStr"/>
       <c r="AA22" s="13" t="inlineStr"/>
@@ -3271,7 +3139,7 @@
       </c>
       <c r="N23" s="11" t="inlineStr">
         <is>
-          <t>8II, 8I</t>
+          <t>4II, 8I</t>
         </is>
       </c>
       <c r="O23" s="12" t="inlineStr"/>
@@ -3283,27 +3151,15 @@
       <c r="Q23" s="12" t="inlineStr"/>
       <c r="R23" s="11" t="inlineStr"/>
       <c r="S23" s="12" t="inlineStr"/>
-      <c r="T23" s="11" t="inlineStr">
-        <is>
-          <t>4II, 8I</t>
-        </is>
-      </c>
+      <c r="T23" s="11" t="inlineStr"/>
       <c r="U23" s="12" t="inlineStr">
         <is>
-          <t>A3, D3</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="V23" s="11" t="inlineStr"/>
-      <c r="W23" s="12" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
-      <c r="X23" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+      <c r="W23" s="12" t="inlineStr"/>
+      <c r="X23" s="11" t="inlineStr"/>
       <c r="Y23" s="12" t="inlineStr"/>
       <c r="Z23" s="11" t="inlineStr"/>
       <c r="AA23" s="13" t="inlineStr"/>
@@ -3350,11 +3206,15 @@
           <t>2I, 2II</t>
         </is>
       </c>
-      <c r="L24" s="11" t="inlineStr"/>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="M24" s="12" t="inlineStr"/>
       <c r="N24" s="11" t="inlineStr">
         <is>
-          <t>8II</t>
+          <t>4II</t>
         </is>
       </c>
       <c r="O24" s="12" t="inlineStr"/>
@@ -3371,25 +3231,21 @@
       </c>
       <c r="S24" s="12" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>1I, A1</t>
         </is>
       </c>
       <c r="T24" s="11" t="inlineStr">
         <is>
-          <t>4II, 8II</t>
+          <t>8II</t>
         </is>
       </c>
       <c r="U24" s="12" t="inlineStr">
         <is>
-          <t>A3, D3</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="V24" s="11" t="inlineStr"/>
-      <c r="W24" s="12" t="inlineStr">
-        <is>
-          <t>1II/3II</t>
-        </is>
-      </c>
+      <c r="W24" s="12" t="inlineStr"/>
       <c r="X24" s="11" t="inlineStr"/>
       <c r="Y24" s="12" t="inlineStr"/>
       <c r="Z24" s="11" t="inlineStr"/>
@@ -3441,7 +3297,7 @@
       <c r="M25" s="12" t="inlineStr"/>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>8II</t>
+          <t>4II</t>
         </is>
       </c>
       <c r="O25" s="12" t="inlineStr"/>
@@ -3455,20 +3311,16 @@
       <c r="S25" s="12" t="inlineStr"/>
       <c r="T25" s="11" t="inlineStr">
         <is>
-          <t>4II, 8II</t>
+          <t>8II</t>
         </is>
       </c>
       <c r="U25" s="12" t="inlineStr">
         <is>
-          <t>A3, D3</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="V25" s="11" t="inlineStr"/>
-      <c r="W25" s="12" t="inlineStr">
-        <is>
-          <t>1II/3II</t>
-        </is>
-      </c>
+      <c r="W25" s="12" t="inlineStr"/>
       <c r="X25" s="11" t="inlineStr"/>
       <c r="Y25" s="12" t="inlineStr"/>
       <c r="Z25" s="11" t="inlineStr"/>
@@ -6192,7 +6044,11 @@
       <c r="K6" s="12" t="inlineStr"/>
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>4II, 2I</t>
+        </is>
+      </c>
       <c r="O6" s="12" t="inlineStr">
         <is>
           <t>8II</t>
@@ -6206,16 +6062,8 @@
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr">
-        <is>
-          <t>4II, 2I</t>
-        </is>
-      </c>
-      <c r="U6" s="12" t="inlineStr">
-        <is>
-          <t>D3, D1</t>
-        </is>
-      </c>
+      <c r="T6" s="11" t="inlineStr"/>
+      <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
@@ -6267,7 +6115,11 @@
       <c r="K7" s="12" t="inlineStr"/>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>4II, 2I</t>
+        </is>
+      </c>
       <c r="O7" s="12" t="inlineStr">
         <is>
           <t>8II</t>
@@ -6277,16 +6129,8 @@
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr">
-        <is>
-          <t>4II, 2I</t>
-        </is>
-      </c>
-      <c r="U7" s="12" t="inlineStr">
-        <is>
-          <t>D3, D1</t>
-        </is>
-      </c>
+      <c r="T7" s="11" t="inlineStr"/>
+      <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
@@ -6348,7 +6192,7 @@
       <c r="M8" s="12" t="inlineStr"/>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>8I, 8II</t>
+          <t>8I, 4II, 2I</t>
         </is>
       </c>
       <c r="O8" s="12" t="inlineStr"/>
@@ -6360,16 +6204,8 @@
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr">
-        <is>
-          <t>4II, 2I</t>
-        </is>
-      </c>
-      <c r="U8" s="12" t="inlineStr">
-        <is>
-          <t>D3, D1</t>
-        </is>
-      </c>
+      <c r="T8" s="11" t="inlineStr"/>
+      <c r="U8" s="12" t="inlineStr"/>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
       <c r="X8" s="11" t="inlineStr"/>
@@ -6407,46 +6243,50 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>8II+</t>
+          <t>8II-</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>8II, 4I, 2II</t>
+          <t>2II</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8II, 8I, 4II, 4I</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>8I, 8II</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O9" s="12" t="inlineStr"/>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
-      <c r="R9" s="11" t="inlineStr"/>
+      <c r="R9" s="11" t="inlineStr">
+        <is>
+          <t>8II, 8I, D3, 4II, 4I, 2II, A3</t>
+        </is>
+      </c>
       <c r="S9" s="12" t="inlineStr"/>
       <c r="T9" s="11" t="inlineStr">
         <is>
-          <t>4II, 2I</t>
+          <t>2I</t>
         </is>
       </c>
       <c r="U9" s="12" t="inlineStr">
         <is>
-          <t>D3, D1</t>
+          <t>A2, D1</t>
         </is>
       </c>
       <c r="V9" s="11" t="inlineStr"/>
@@ -6486,61 +6326,41 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr"/>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>8II-</t>
+          <t>8II+</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>2II</t>
+          <t>8II, 4I, 2II</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>8II, 8I, 4II, 4I</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O10" s="12" t="inlineStr">
-        <is>
-          <t>2I, 8II</t>
-        </is>
-      </c>
+          <t>8I, 4II, 2I</t>
+        </is>
+      </c>
+      <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
-      <c r="R10" s="11" t="inlineStr">
-        <is>
-          <t>8II, 8I, D3, 4II, 4I, 2II, A3</t>
-        </is>
-      </c>
+      <c r="R10" s="11" t="inlineStr"/>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr">
-        <is>
-          <t>2I, 2I</t>
-        </is>
-      </c>
-      <c r="U10" s="12" t="inlineStr">
-        <is>
-          <t>A2, D1</t>
-        </is>
-      </c>
-      <c r="V10" s="11" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
+      <c r="T10" s="11" t="inlineStr"/>
+      <c r="U10" s="12" t="inlineStr"/>
+      <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
       <c r="Y10" s="12" t="inlineStr"/>
@@ -6604,18 +6424,14 @@
           <t>6</t>
         </is>
       </c>
-      <c r="O11" s="12" t="inlineStr">
-        <is>
-          <t>2I, 8II</t>
-        </is>
-      </c>
+      <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
       <c r="T11" s="11" t="inlineStr">
         <is>
-          <t>2I, 2I</t>
+          <t>2I</t>
         </is>
       </c>
       <c r="U11" s="12" t="inlineStr">
@@ -6623,11 +6439,7 @@
           <t>A2, D1</t>
         </is>
       </c>
-      <c r="V11" s="11" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
+      <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="11" t="inlineStr"/>
       <c r="Y11" s="12" t="inlineStr"/>
@@ -6687,11 +6499,7 @@
           <t>8II</t>
         </is>
       </c>
-      <c r="O12" s="12" t="inlineStr">
-        <is>
-          <t>2I, 8II</t>
-        </is>
-      </c>
+      <c r="O12" s="12" t="inlineStr"/>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr">
@@ -6702,7 +6510,7 @@
       <c r="S12" s="12" t="inlineStr"/>
       <c r="T12" s="11" t="inlineStr">
         <is>
-          <t>2I, 2I</t>
+          <t>2I</t>
         </is>
       </c>
       <c r="U12" s="12" t="inlineStr">
@@ -6710,11 +6518,7 @@
           <t>A2, D1</t>
         </is>
       </c>
-      <c r="V12" s="11" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
+      <c r="V12" s="11" t="inlineStr"/>
       <c r="W12" s="12" t="inlineStr"/>
       <c r="X12" s="11" t="inlineStr"/>
       <c r="Y12" s="12" t="inlineStr"/>
@@ -6774,18 +6578,14 @@
           <t>8II</t>
         </is>
       </c>
-      <c r="O13" s="12" t="inlineStr">
-        <is>
-          <t>2I, 8II</t>
-        </is>
-      </c>
+      <c r="O13" s="12" t="inlineStr"/>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
       <c r="T13" s="11" t="inlineStr">
         <is>
-          <t>2I, 2I</t>
+          <t>2I</t>
         </is>
       </c>
       <c r="U13" s="12" t="inlineStr">
@@ -6793,11 +6593,7 @@
           <t>A2, D1</t>
         </is>
       </c>
-      <c r="V13" s="11" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
+      <c r="V13" s="11" t="inlineStr"/>
       <c r="W13" s="12" t="inlineStr"/>
       <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
@@ -10025,7 +9821,11 @@
           <t>8II</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr"/>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="N6" s="11" t="inlineStr">
         <is>
           <t>1I</t>
@@ -10051,11 +9851,7 @@
       <c r="T6" s="11" t="inlineStr"/>
       <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
-      <c r="W6" s="12" t="inlineStr">
-        <is>
-          <t>8I</t>
-        </is>
-      </c>
+      <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
       <c r="Y6" s="12" t="inlineStr"/>
       <c r="Z6" s="11" t="inlineStr"/>
@@ -10087,12 +9883,12 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>8II+</t>
+          <t>8II-</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr"/>
@@ -10103,12 +9899,12 @@
           <t>3I, 3II</t>
         </is>
       </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>8II</t>
-        </is>
-      </c>
-      <c r="M7" s="12" t="inlineStr"/>
+      <c r="L7" s="11" t="inlineStr"/>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>8II, 8I</t>
+        </is>
+      </c>
       <c r="N7" s="11" t="inlineStr">
         <is>
           <t>1I</t>
@@ -10117,20 +9913,24 @@
       <c r="O7" s="12" t="inlineStr"/>
       <c r="P7" s="11" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr"/>
-      <c r="R7" s="11" t="inlineStr"/>
-      <c r="S7" s="12" t="inlineStr"/>
+      <c r="R7" s="11" t="inlineStr">
+        <is>
+          <t>D4, 3I, 1II/3II, III</t>
+        </is>
+      </c>
+      <c r="S7" s="12" t="inlineStr">
+        <is>
+          <t>8II, 8I</t>
+        </is>
+      </c>
       <c r="T7" s="11" t="inlineStr"/>
       <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
-      <c r="W7" s="12" t="inlineStr">
-        <is>
-          <t>8I</t>
-        </is>
-      </c>
+      <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
       <c r="Y7" s="12" t="inlineStr"/>
       <c r="Z7" s="11" t="inlineStr"/>
@@ -10162,12 +9962,12 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>8II-</t>
+          <t>8II+</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr"/>
@@ -10178,12 +9978,12 @@
           <t>3I, 3II</t>
         </is>
       </c>
-      <c r="L8" s="11" t="inlineStr"/>
-      <c r="M8" s="12" t="inlineStr">
+      <c r="L8" s="11" t="inlineStr">
         <is>
           <t>8II</t>
         </is>
       </c>
+      <c r="M8" s="12" t="inlineStr"/>
       <c r="N8" s="11" t="inlineStr">
         <is>
           <t>1I</t>
@@ -10192,29 +9992,17 @@
       <c r="O8" s="12" t="inlineStr"/>
       <c r="P8" s="11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr"/>
-      <c r="R8" s="11" t="inlineStr">
-        <is>
-          <t>D4, 3I, 1II/3II, III</t>
-        </is>
-      </c>
-      <c r="S8" s="12" t="inlineStr">
-        <is>
-          <t>8II, 8I</t>
-        </is>
-      </c>
+      <c r="R8" s="11" t="inlineStr"/>
+      <c r="S8" s="12" t="inlineStr"/>
       <c r="T8" s="11" t="inlineStr"/>
       <c r="U8" s="12" t="inlineStr"/>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
-      <c r="X8" s="11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="X8" s="11" t="inlineStr"/>
       <c r="Y8" s="12" t="inlineStr"/>
       <c r="Z8" s="11" t="inlineStr"/>
       <c r="AA8" s="13" t="inlineStr"/>
@@ -10285,11 +10073,7 @@
       <c r="U9" s="12" t="inlineStr"/>
       <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
-      <c r="X9" s="11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="X9" s="11" t="inlineStr"/>
       <c r="Y9" s="12" t="inlineStr"/>
       <c r="Z9" s="11" t="inlineStr"/>
       <c r="AA9" s="13" t="inlineStr"/>
@@ -10357,18 +10141,14 @@
       </c>
       <c r="S10" s="12" t="inlineStr">
         <is>
-          <t>8I</t>
+          <t>8I, D3</t>
         </is>
       </c>
       <c r="T10" s="11" t="inlineStr"/>
       <c r="U10" s="12" t="inlineStr"/>
       <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
-      <c r="X10" s="11" t="inlineStr">
-        <is>
-          <t>8II</t>
-        </is>
-      </c>
+      <c r="X10" s="11" t="inlineStr"/>
       <c r="Y10" s="12" t="inlineStr"/>
       <c r="Z10" s="11" t="inlineStr"/>
       <c r="AA10" s="13" t="inlineStr"/>
@@ -10431,11 +10211,7 @@
       <c r="U11" s="12" t="inlineStr"/>
       <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="12" t="inlineStr"/>
-      <c r="X11" s="11" t="inlineStr">
-        <is>
-          <t>8II</t>
-        </is>
-      </c>
+      <c r="X11" s="11" t="inlineStr"/>
       <c r="Y11" s="12" t="inlineStr"/>
       <c r="Z11" s="11" t="inlineStr"/>
       <c r="AA11" s="13" t="inlineStr"/>
@@ -10488,14 +10264,10 @@
         </is>
       </c>
       <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="N12" s="11" t="inlineStr"/>
+      <c r="O12" s="12" t="inlineStr">
         <is>
           <t>8II</t>
-        </is>
-      </c>
-      <c r="O12" s="12" t="inlineStr">
-        <is>
-          <t>8II, 2I</t>
         </is>
       </c>
       <c r="P12" s="11" t="inlineStr">
@@ -10516,7 +10288,7 @@
       </c>
       <c r="T12" s="11" t="inlineStr">
         <is>
-          <t>2I, 2I</t>
+          <t>2I</t>
         </is>
       </c>
       <c r="U12" s="12" t="inlineStr">
@@ -10524,16 +10296,8 @@
           <t>D1, A2, 8II</t>
         </is>
       </c>
-      <c r="V12" s="11" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="W12" s="12" t="inlineStr">
-        <is>
-          <t>1II/3II</t>
-        </is>
-      </c>
+      <c r="V12" s="11" t="inlineStr"/>
+      <c r="W12" s="12" t="inlineStr"/>
       <c r="X12" s="11" t="inlineStr"/>
       <c r="Y12" s="12" t="inlineStr"/>
       <c r="Z12" s="11" t="inlineStr"/>
@@ -10583,14 +10347,10 @@
       </c>
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="N13" s="11" t="inlineStr"/>
+      <c r="O13" s="12" t="inlineStr">
         <is>
           <t>8II</t>
-        </is>
-      </c>
-      <c r="O13" s="12" t="inlineStr">
-        <is>
-          <t>8II, 2I</t>
         </is>
       </c>
       <c r="P13" s="11" t="inlineStr">
@@ -10603,7 +10363,7 @@
       <c r="S13" s="12" t="inlineStr"/>
       <c r="T13" s="11" t="inlineStr">
         <is>
-          <t>2I, 2I</t>
+          <t>2I</t>
         </is>
       </c>
       <c r="U13" s="12" t="inlineStr">
@@ -10611,16 +10371,8 @@
           <t>D1, A2, 8II</t>
         </is>
       </c>
-      <c r="V13" s="11" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="W13" s="12" t="inlineStr">
-        <is>
-          <t>1II/3II</t>
-        </is>
-      </c>
+      <c r="V13" s="11" t="inlineStr"/>
+      <c r="W13" s="12" t="inlineStr"/>
       <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
       <c r="Z13" s="11" t="inlineStr"/>
@@ -10684,13 +10436,13 @@
       <c r="M14" s="12" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>8II, 8I</t>
+          <t>2I, 4II, 8I</t>
         </is>
       </c>
       <c r="O14" s="12" t="inlineStr"/>
       <c r="P14" s="11" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>3I, 1I</t>
         </is>
       </c>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -10704,27 +10456,11 @@
           <t>1II/3II</t>
         </is>
       </c>
-      <c r="T14" s="11" t="inlineStr">
-        <is>
-          <t>2I, 4II, 8I</t>
-        </is>
-      </c>
-      <c r="U14" s="12" t="inlineStr">
-        <is>
-          <t>D1, D3</t>
-        </is>
-      </c>
+      <c r="T14" s="11" t="inlineStr"/>
+      <c r="U14" s="12" t="inlineStr"/>
       <c r="V14" s="11" t="inlineStr"/>
-      <c r="W14" s="12" t="inlineStr">
-        <is>
-          <t>3I, 1I</t>
-        </is>
-      </c>
-      <c r="X14" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+      <c r="W14" s="12" t="inlineStr"/>
+      <c r="X14" s="11" t="inlineStr"/>
       <c r="Y14" s="12" t="inlineStr"/>
       <c r="Z14" s="11" t="inlineStr"/>
       <c r="AA14" s="13" t="inlineStr"/>
@@ -10755,12 +10491,12 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>3II+</t>
+          <t>3II+/1II-</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -10784,42 +10520,38 @@
           <t>3II</t>
         </is>
       </c>
-      <c r="M15" s="12" t="inlineStr"/>
+      <c r="M15" s="12" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>8II, 8I</t>
+          <t>2I, 4II, 8I</t>
         </is>
       </c>
       <c r="O15" s="12" t="inlineStr"/>
       <c r="P15" s="11" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>3I</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr"/>
-      <c r="R15" s="11" t="inlineStr"/>
-      <c r="S15" s="12" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr">
-        <is>
-          <t>2I, 4II, 8I</t>
-        </is>
-      </c>
-      <c r="U15" s="12" t="inlineStr">
-        <is>
-          <t>D1, D3</t>
-        </is>
-      </c>
+      <c r="R15" s="11" t="inlineStr">
+        <is>
+          <t>A3, 2II, 4I, A2, 6, 8II, III</t>
+        </is>
+      </c>
+      <c r="S15" s="12" t="inlineStr">
+        <is>
+          <t>1II/3II, 1I</t>
+        </is>
+      </c>
+      <c r="T15" s="11" t="inlineStr"/>
+      <c r="U15" s="12" t="inlineStr"/>
       <c r="V15" s="11" t="inlineStr"/>
-      <c r="W15" s="12" t="inlineStr">
-        <is>
-          <t>3I, 1I</t>
-        </is>
-      </c>
-      <c r="X15" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+      <c r="W15" s="12" t="inlineStr"/>
+      <c r="X15" s="11" t="inlineStr"/>
       <c r="Y15" s="12" t="inlineStr"/>
       <c r="Z15" s="11" t="inlineStr"/>
       <c r="AA15" s="13" t="inlineStr"/>
@@ -10855,7 +10587,7 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>3II+/1II-</t>
+          <t>3II-</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -10874,23 +10606,23 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>3II</t>
-        </is>
-      </c>
+      <c r="L16" s="11" t="inlineStr"/>
       <c r="M16" s="12" t="inlineStr">
         <is>
-          <t>1II</t>
+          <t>3II, 3I</t>
         </is>
       </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>8II, 8I</t>
+          <t>2I, 4II, 8I</t>
         </is>
       </c>
       <c r="O16" s="12" t="inlineStr"/>
-      <c r="P16" s="11" t="inlineStr"/>
+      <c r="P16" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr">
         <is>
@@ -10899,25 +10631,13 @@
       </c>
       <c r="S16" s="12" t="inlineStr">
         <is>
-          <t>1II/3II</t>
-        </is>
-      </c>
-      <c r="T16" s="11" t="inlineStr">
-        <is>
-          <t>2I, 4II, 8I</t>
-        </is>
-      </c>
-      <c r="U16" s="12" t="inlineStr">
-        <is>
-          <t>D1, D3</t>
-        </is>
-      </c>
+          <t>1II/3II, 3I, D4</t>
+        </is>
+      </c>
+      <c r="T16" s="11" t="inlineStr"/>
+      <c r="U16" s="12" t="inlineStr"/>
       <c r="V16" s="11" t="inlineStr"/>
-      <c r="W16" s="12" t="inlineStr">
-        <is>
-          <t>3I</t>
-        </is>
-      </c>
+      <c r="W16" s="12" t="inlineStr"/>
       <c r="X16" s="11" t="inlineStr"/>
       <c r="Y16" s="12" t="inlineStr"/>
       <c r="Z16" s="11" t="inlineStr"/>
@@ -10954,74 +10674,66 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>3II-</t>
+          <t>3II+/1II+</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>4I+</t>
+          <t>4I-</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>2II, 4I, 8II</t>
+          <t>2II</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
+          <t>4I, 4II, 8I, 8II</t>
+        </is>
+      </c>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
+          <t>3II, 1II</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="inlineStr"/>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="L17" s="11" t="inlineStr"/>
-      <c r="M17" s="12" t="inlineStr">
-        <is>
-          <t>3II, 3I</t>
-        </is>
-      </c>
-      <c r="N17" s="11" t="inlineStr">
-        <is>
-          <t>8II, 8I</t>
         </is>
       </c>
       <c r="O17" s="12" t="inlineStr"/>
       <c r="P17" s="11" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>3I, 1I</t>
         </is>
       </c>
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>A3, 2II, 4I, A2, 6, 8II, III</t>
+          <t>A3, 2II, 4I, 4II, D3, 8I, 8II, III</t>
         </is>
       </c>
       <c r="S17" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 3I</t>
+          <t>1II/3II</t>
         </is>
       </c>
       <c r="T17" s="11" t="inlineStr">
         <is>
-          <t>2I, 4II, 8I</t>
+          <t>2I</t>
         </is>
       </c>
       <c r="U17" s="12" t="inlineStr">
         <is>
-          <t>D1, D3</t>
+          <t>D1, A2</t>
         </is>
       </c>
       <c r="V17" s="11" t="inlineStr"/>
-      <c r="W17" s="12" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
-      <c r="X17" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+      <c r="W17" s="12" t="inlineStr"/>
+      <c r="X17" s="11" t="inlineStr"/>
       <c r="Y17" s="12" t="inlineStr"/>
       <c r="Z17" s="11" t="inlineStr"/>
       <c r="AA17" s="13" t="inlineStr"/>
@@ -11052,71 +10764,75 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>3II-</t>
+          <t>3II+/1II-</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>4I+</t>
+          <t>4I-</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr"/>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>2II, 4I, 8II</t>
+          <t>2II</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
+          <t>4I, 4II, 8I, 8II</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="M18" s="12" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="L18" s="11" t="inlineStr"/>
-      <c r="M18" s="12" t="inlineStr">
-        <is>
-          <t>3II</t>
-        </is>
-      </c>
-      <c r="N18" s="11" t="inlineStr">
-        <is>
-          <t>8II, 8I</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr"/>
       <c r="P18" s="11" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>3I</t>
         </is>
       </c>
       <c r="Q18" s="12" t="inlineStr"/>
-      <c r="R18" s="11" t="inlineStr"/>
-      <c r="S18" s="12" t="inlineStr"/>
+      <c r="R18" s="11" t="inlineStr">
+        <is>
+          <t>A3, 2II, 4I, 4II, D3, 8I, 8II, III</t>
+        </is>
+      </c>
+      <c r="S18" s="12" t="inlineStr">
+        <is>
+          <t>1II/3II, 1I</t>
+        </is>
+      </c>
       <c r="T18" s="11" t="inlineStr">
         <is>
-          <t>2I, 4II, 8I</t>
+          <t>2I</t>
         </is>
       </c>
       <c r="U18" s="12" t="inlineStr">
         <is>
-          <t>D1, D3</t>
+          <t>D1, A2</t>
         </is>
       </c>
       <c r="V18" s="11" t="inlineStr"/>
-      <c r="W18" s="12" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
-      <c r="X18" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+      <c r="W18" s="12" t="inlineStr"/>
+      <c r="X18" s="11" t="inlineStr"/>
       <c r="Y18" s="12" t="inlineStr"/>
       <c r="Z18" s="11" t="inlineStr"/>
       <c r="AA18" s="13" t="inlineStr"/>
@@ -11152,7 +10868,7 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>3II+/1II+</t>
+          <t>3II-</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -11171,22 +10887,18 @@
           <t>4I, 4II, 8I, 8II</t>
         </is>
       </c>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>3II, 1II</t>
-        </is>
-      </c>
-      <c r="M19" s="12" t="inlineStr"/>
+      <c r="L19" s="11" t="inlineStr"/>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>3II, 3I</t>
+        </is>
+      </c>
       <c r="N19" s="11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O19" s="12" t="inlineStr">
-        <is>
-          <t>8II, 2I</t>
-        </is>
-      </c>
+      <c r="O19" s="12" t="inlineStr"/>
       <c r="P19" s="11" t="inlineStr">
         <is>
           <t>1I</t>
@@ -11200,34 +10912,22 @@
       </c>
       <c r="S19" s="12" t="inlineStr">
         <is>
-          <t>1II/3II</t>
+          <t>1II/3II, 3I, D4</t>
         </is>
       </c>
       <c r="T19" s="11" t="inlineStr">
         <is>
-          <t>2I, 2I</t>
+          <t>2I</t>
         </is>
       </c>
       <c r="U19" s="12" t="inlineStr">
         <is>
-          <t>D1, A2, 6</t>
-        </is>
-      </c>
-      <c r="V19" s="11" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="W19" s="12" t="inlineStr">
-        <is>
-          <t>3I, 1I</t>
-        </is>
-      </c>
-      <c r="X19" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+          <t>D1, A2</t>
+        </is>
+      </c>
+      <c r="V19" s="11" t="inlineStr"/>
+      <c r="W19" s="12" t="inlineStr"/>
+      <c r="X19" s="11" t="inlineStr"/>
       <c r="Y19" s="12" t="inlineStr"/>
       <c r="Z19" s="11" t="inlineStr"/>
       <c r="AA19" s="13" t="inlineStr"/>
@@ -11268,18 +10968,18 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>4I-</t>
+          <t>4I+</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr"/>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>2II</t>
+          <t>2II, 4I, 8II</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>4I, 4II, 8I, 8II</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L20" s="11" t="inlineStr">
@@ -11290,47 +10990,23 @@
       <c r="M20" s="12" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O20" s="12" t="inlineStr">
-        <is>
-          <t>8II, 2I</t>
-        </is>
-      </c>
+          <t>2I, 4II, 8I</t>
+        </is>
+      </c>
+      <c r="O20" s="12" t="inlineStr"/>
       <c r="P20" s="11" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>3I, 1I</t>
         </is>
       </c>
       <c r="Q20" s="12" t="inlineStr"/>
       <c r="R20" s="11" t="inlineStr"/>
       <c r="S20" s="12" t="inlineStr"/>
-      <c r="T20" s="11" t="inlineStr">
-        <is>
-          <t>2I, 2I</t>
-        </is>
-      </c>
-      <c r="U20" s="12" t="inlineStr">
-        <is>
-          <t>D1, A2, 6</t>
-        </is>
-      </c>
-      <c r="V20" s="11" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="W20" s="12" t="inlineStr">
-        <is>
-          <t>3I, 1I</t>
-        </is>
-      </c>
-      <c r="X20" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+      <c r="T20" s="11" t="inlineStr"/>
+      <c r="U20" s="12" t="inlineStr"/>
+      <c r="V20" s="11" t="inlineStr"/>
+      <c r="W20" s="12" t="inlineStr"/>
+      <c r="X20" s="11" t="inlineStr"/>
       <c r="Y20" s="12" t="inlineStr"/>
       <c r="Z20" s="11" t="inlineStr"/>
       <c r="AA20" s="13" t="inlineStr"/>
@@ -11361,82 +11037,54 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>3II+/1II-</t>
+          <t>3II-</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>4I-</t>
+          <t>4I+</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr"/>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>2II</t>
+          <t>2II, 4I, 8II</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>4I, 4II, 8I, 8II</t>
-        </is>
-      </c>
-      <c r="L21" s="11" t="inlineStr">
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr"/>
+      <c r="M21" s="12" t="inlineStr">
         <is>
           <t>3II</t>
         </is>
       </c>
-      <c r="M21" s="12" t="inlineStr">
-        <is>
-          <t>1II</t>
-        </is>
-      </c>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O21" s="12" t="inlineStr">
-        <is>
-          <t>8II, 2I</t>
-        </is>
-      </c>
-      <c r="P21" s="11" t="inlineStr"/>
+          <t>2I, 4II, 8I</t>
+        </is>
+      </c>
+      <c r="O21" s="12" t="inlineStr"/>
+      <c r="P21" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q21" s="12" t="inlineStr"/>
-      <c r="R21" s="11" t="inlineStr">
-        <is>
-          <t>A3, 2II, 4I, 4II, D3, 8I, 8II, III</t>
-        </is>
-      </c>
-      <c r="S21" s="12" t="inlineStr">
-        <is>
-          <t>1II/3II</t>
-        </is>
-      </c>
-      <c r="T21" s="11" t="inlineStr">
-        <is>
-          <t>2I, 2I</t>
-        </is>
-      </c>
-      <c r="U21" s="12" t="inlineStr">
-        <is>
-          <t>D1, A2, 6</t>
-        </is>
-      </c>
-      <c r="V21" s="11" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="W21" s="12" t="inlineStr">
-        <is>
-          <t>3I</t>
-        </is>
-      </c>
+      <c r="R21" s="11" t="inlineStr"/>
+      <c r="S21" s="12" t="inlineStr"/>
+      <c r="T21" s="11" t="inlineStr"/>
+      <c r="U21" s="12" t="inlineStr"/>
+      <c r="V21" s="11" t="inlineStr"/>
+      <c r="W21" s="12" t="inlineStr"/>
       <c r="X21" s="11" t="inlineStr"/>
       <c r="Y21" s="12" t="inlineStr"/>
       <c r="Z21" s="11" t="inlineStr"/>
@@ -11468,12 +11116,12 @@
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>3II-</t>
+          <t>3II+</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -11492,63 +11140,39 @@
           <t>4I, 4II, 8I, 8II</t>
         </is>
       </c>
-      <c r="L22" s="11" t="inlineStr"/>
-      <c r="M22" s="12" t="inlineStr">
-        <is>
-          <t>3II, 3I</t>
-        </is>
-      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="M22" s="12" t="inlineStr"/>
       <c r="N22" s="11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O22" s="12" t="inlineStr">
-        <is>
-          <t>8II, 2I</t>
-        </is>
-      </c>
+      <c r="O22" s="12" t="inlineStr"/>
       <c r="P22" s="11" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>3I, 1I</t>
         </is>
       </c>
       <c r="Q22" s="12" t="inlineStr"/>
-      <c r="R22" s="11" t="inlineStr">
-        <is>
-          <t>A3, 2II, 4I, 4II, D3, 8I, 8II, III</t>
-        </is>
-      </c>
-      <c r="S22" s="12" t="inlineStr">
-        <is>
-          <t>1II/3II, 3I</t>
-        </is>
-      </c>
+      <c r="R22" s="11" t="inlineStr"/>
+      <c r="S22" s="12" t="inlineStr"/>
       <c r="T22" s="11" t="inlineStr">
         <is>
-          <t>2I, 2I</t>
+          <t>2I</t>
         </is>
       </c>
       <c r="U22" s="12" t="inlineStr">
         <is>
-          <t>D1, A2, 6</t>
-        </is>
-      </c>
-      <c r="V22" s="11" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="W22" s="12" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
-      <c r="X22" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+          <t>D1, A2</t>
+        </is>
+      </c>
+      <c r="V22" s="11" t="inlineStr"/>
+      <c r="W22" s="12" t="inlineStr"/>
+      <c r="X22" s="11" t="inlineStr"/>
       <c r="Y22" s="12" t="inlineStr"/>
       <c r="Z22" s="11" t="inlineStr"/>
       <c r="AA22" s="13" t="inlineStr"/>
@@ -11614,11 +11238,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="O23" s="12" t="inlineStr">
-        <is>
-          <t>8II, 2I</t>
-        </is>
-      </c>
+      <c r="O23" s="12" t="inlineStr"/>
       <c r="P23" s="11" t="inlineStr">
         <is>
           <t>1I</t>
@@ -11629,29 +11249,17 @@
       <c r="S23" s="12" t="inlineStr"/>
       <c r="T23" s="11" t="inlineStr">
         <is>
-          <t>2I, 2I</t>
+          <t>2I</t>
         </is>
       </c>
       <c r="U23" s="12" t="inlineStr">
         <is>
-          <t>D1, A2, 6</t>
-        </is>
-      </c>
-      <c r="V23" s="11" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="W23" s="12" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
-      <c r="X23" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+          <t>D1, A2</t>
+        </is>
+      </c>
+      <c r="V23" s="11" t="inlineStr"/>
+      <c r="W23" s="12" t="inlineStr"/>
+      <c r="X23" s="11" t="inlineStr"/>
       <c r="Y23" s="12" t="inlineStr"/>
       <c r="Z23" s="11" t="inlineStr"/>
       <c r="AA23" s="13" t="inlineStr"/>
@@ -11694,11 +11302,15 @@
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr"/>
-      <c r="L24" s="11" t="inlineStr"/>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="M24" s="12" t="inlineStr"/>
       <c r="N24" s="11" t="inlineStr">
         <is>
-          <t>8II</t>
+          <t>2I, 4II</t>
         </is>
       </c>
       <c r="O24" s="12" t="inlineStr"/>
@@ -11715,25 +11327,17 @@
       </c>
       <c r="S24" s="12" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>1I, A1</t>
         </is>
       </c>
       <c r="T24" s="11" t="inlineStr">
         <is>
-          <t>2I, 4II, 8II</t>
-        </is>
-      </c>
-      <c r="U24" s="12" t="inlineStr">
-        <is>
-          <t>D1, D3</t>
-        </is>
-      </c>
+          <t>8II</t>
+        </is>
+      </c>
+      <c r="U24" s="12" t="inlineStr"/>
       <c r="V24" s="11" t="inlineStr"/>
-      <c r="W24" s="12" t="inlineStr">
-        <is>
-          <t>1II/3II</t>
-        </is>
-      </c>
+      <c r="W24" s="12" t="inlineStr"/>
       <c r="X24" s="11" t="inlineStr"/>
       <c r="Y24" s="12" t="inlineStr"/>
       <c r="Z24" s="11" t="inlineStr"/>
@@ -11781,7 +11385,7 @@
       <c r="M25" s="12" t="inlineStr"/>
       <c r="N25" s="11" t="inlineStr">
         <is>
-          <t>8II</t>
+          <t>2I, 4II</t>
         </is>
       </c>
       <c r="O25" s="12" t="inlineStr"/>
@@ -11795,20 +11399,12 @@
       <c r="S25" s="12" t="inlineStr"/>
       <c r="T25" s="11" t="inlineStr">
         <is>
-          <t>2I, 4II, 8II</t>
-        </is>
-      </c>
-      <c r="U25" s="12" t="inlineStr">
-        <is>
-          <t>D1, D3</t>
-        </is>
-      </c>
+          <t>8II</t>
+        </is>
+      </c>
+      <c r="U25" s="12" t="inlineStr"/>
       <c r="V25" s="11" t="inlineStr"/>
-      <c r="W25" s="12" t="inlineStr">
-        <is>
-          <t>1II/3II</t>
-        </is>
-      </c>
+      <c r="W25" s="12" t="inlineStr"/>
       <c r="X25" s="11" t="inlineStr"/>
       <c r="Y25" s="12" t="inlineStr"/>
       <c r="Z25" s="11" t="inlineStr"/>
@@ -14540,7 +14136,11 @@
       </c>
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
       <c r="O6" s="12" t="inlineStr">
         <is>
           <t>8II</t>
@@ -14554,14 +14154,10 @@
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr">
-        <is>
-          <t>4II</t>
-        </is>
-      </c>
+      <c r="T6" s="11" t="inlineStr"/>
       <c r="U6" s="12" t="inlineStr">
         <is>
-          <t>D3, A3</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="V6" s="11" t="inlineStr"/>
@@ -14623,7 +14219,11 @@
       </c>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>4II</t>
+        </is>
+      </c>
       <c r="O7" s="12" t="inlineStr">
         <is>
           <t>8II</t>
@@ -14633,14 +14233,10 @@
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr">
-        <is>
-          <t>4II</t>
-        </is>
-      </c>
+      <c r="T7" s="11" t="inlineStr"/>
       <c r="U7" s="12" t="inlineStr">
         <is>
-          <t>D3, A3</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="V7" s="11" t="inlineStr"/>
@@ -14708,7 +14304,7 @@
       <c r="M8" s="12" t="inlineStr"/>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>8I, 8II</t>
+          <t>8I, 4II</t>
         </is>
       </c>
       <c r="O8" s="12" t="inlineStr"/>
@@ -14720,14 +14316,10 @@
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr">
-        <is>
-          <t>4II</t>
-        </is>
-      </c>
+      <c r="T8" s="11" t="inlineStr"/>
       <c r="U8" s="12" t="inlineStr">
         <is>
-          <t>D3, A3</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="V8" s="11" t="inlineStr"/>
@@ -14767,13 +14359,13 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>8II+</t>
+          <t>8II-</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
@@ -14783,36 +14375,32 @@
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>8II, 4I</t>
+          <t>4II, 2I</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>6, 2II, 2I</t>
+          <t>8II, 8I</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>8I, 8II</t>
+          <t>6, 4I, 2II</t>
         </is>
       </c>
       <c r="O9" s="12" t="inlineStr"/>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
-      <c r="R9" s="11" t="inlineStr"/>
+      <c r="R9" s="11" t="inlineStr">
+        <is>
+          <t>8II, 8I, D3, 4II, 2I, D1</t>
+        </is>
+      </c>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr">
-        <is>
-          <t>4II</t>
-        </is>
-      </c>
-      <c r="U9" s="12" t="inlineStr">
-        <is>
-          <t>D3, A3</t>
-        </is>
-      </c>
+      <c r="T9" s="11" t="inlineStr"/>
+      <c r="U9" s="12" t="inlineStr"/>
       <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
       <c r="X9" s="11" t="inlineStr"/>
@@ -14850,13 +14438,13 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr"/>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>8II-</t>
+          <t>8II+</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
@@ -14866,45 +14454,33 @@
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>4II, 2I</t>
+          <t>8II, 4I</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>8II, 8I</t>
+          <t>6, 2II, 2I</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>6, 4II</t>
-        </is>
-      </c>
-      <c r="O10" s="12" t="inlineStr">
-        <is>
-          <t>8II</t>
-        </is>
-      </c>
+          <t>8I, 4II</t>
+        </is>
+      </c>
+      <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
-      <c r="R10" s="11" t="inlineStr">
-        <is>
-          <t>8II, 8I, D3, 4II, 2I, D1</t>
-        </is>
-      </c>
+      <c r="R10" s="11" t="inlineStr"/>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr">
-        <is>
-          <t>4I, 2II, 4I</t>
-        </is>
-      </c>
-      <c r="U10" s="12" t="inlineStr"/>
-      <c r="V10" s="11" t="inlineStr">
-        <is>
-          <t>4II, A2</t>
-        </is>
-      </c>
+      <c r="T10" s="11" t="inlineStr"/>
+      <c r="U10" s="12" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
       <c r="Y10" s="12" t="inlineStr"/>
@@ -14969,29 +14545,17 @@
       <c r="M11" s="12" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>6, 4II</t>
-        </is>
-      </c>
-      <c r="O11" s="12" t="inlineStr">
-        <is>
-          <t>8II</t>
-        </is>
-      </c>
+          <t>6, 4I, 2II</t>
+        </is>
+      </c>
+      <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr">
-        <is>
-          <t>4I, 2II, 4I</t>
-        </is>
-      </c>
+      <c r="T11" s="11" t="inlineStr"/>
       <c r="U11" s="12" t="inlineStr"/>
-      <c r="V11" s="11" t="inlineStr">
-        <is>
-          <t>4II, A2</t>
-        </is>
-      </c>
+      <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="11" t="inlineStr"/>
       <c r="Y11" s="12" t="inlineStr"/>
@@ -15048,14 +14612,10 @@
       <c r="M12" s="12" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>8II, 4II</t>
-        </is>
-      </c>
-      <c r="O12" s="12" t="inlineStr">
-        <is>
-          <t>8II</t>
-        </is>
-      </c>
+          <t>8II, 4I, 2II</t>
+        </is>
+      </c>
+      <c r="O12" s="12" t="inlineStr"/>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr">
@@ -15064,17 +14624,9 @@
         </is>
       </c>
       <c r="S12" s="12" t="inlineStr"/>
-      <c r="T12" s="11" t="inlineStr">
-        <is>
-          <t>4I, 2II, 4I</t>
-        </is>
-      </c>
+      <c r="T12" s="11" t="inlineStr"/>
       <c r="U12" s="12" t="inlineStr"/>
-      <c r="V12" s="11" t="inlineStr">
-        <is>
-          <t>4II, A2</t>
-        </is>
-      </c>
+      <c r="V12" s="11" t="inlineStr"/>
       <c r="W12" s="12" t="inlineStr"/>
       <c r="X12" s="11" t="inlineStr"/>
       <c r="Y12" s="12" t="inlineStr"/>
@@ -15131,29 +14683,17 @@
       <c r="M13" s="12" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>8II, 4II</t>
-        </is>
-      </c>
-      <c r="O13" s="12" t="inlineStr">
-        <is>
-          <t>8II</t>
-        </is>
-      </c>
+          <t>8II, 4I, 2II</t>
+        </is>
+      </c>
+      <c r="O13" s="12" t="inlineStr"/>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
-      <c r="T13" s="11" t="inlineStr">
-        <is>
-          <t>4I, 2II, 4I</t>
-        </is>
-      </c>
+      <c r="T13" s="11" t="inlineStr"/>
       <c r="U13" s="12" t="inlineStr"/>
-      <c r="V13" s="11" t="inlineStr">
-        <is>
-          <t>4II, A2</t>
-        </is>
-      </c>
+      <c r="V13" s="11" t="inlineStr"/>
       <c r="W13" s="12" t="inlineStr"/>
       <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
@@ -15212,7 +14752,11 @@
       </c>
       <c r="L14" s="11" t="inlineStr"/>
       <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="11" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="O14" s="12" t="inlineStr"/>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -15222,11 +14766,7 @@
         </is>
       </c>
       <c r="S14" s="12" t="inlineStr"/>
-      <c r="T14" s="11" t="inlineStr">
-        <is>
-          <t>3I</t>
-        </is>
-      </c>
+      <c r="T14" s="11" t="inlineStr"/>
       <c r="U14" s="12" t="inlineStr"/>
       <c r="V14" s="11" t="inlineStr"/>
       <c r="W14" s="12" t="inlineStr"/>
@@ -15287,17 +14827,17 @@
       </c>
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="O15" s="12" t="inlineStr"/>
       <c r="P15" s="11" t="inlineStr"/>
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr">
-        <is>
-          <t>3I</t>
-        </is>
-      </c>
+      <c r="T15" s="11" t="inlineStr"/>
       <c r="U15" s="12" t="inlineStr"/>
       <c r="V15" s="11" t="inlineStr"/>
       <c r="W15" s="12" t="inlineStr"/>
@@ -18398,7 +17938,11 @@
       <c r="K6" s="12" t="inlineStr"/>
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>4II, 2I</t>
+        </is>
+      </c>
       <c r="O6" s="12" t="inlineStr">
         <is>
           <t>8II</t>
@@ -18408,16 +17952,8 @@
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr"/>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr">
-        <is>
-          <t>4II, 2I</t>
-        </is>
-      </c>
-      <c r="U6" s="12" t="inlineStr">
-        <is>
-          <t>D3, D1</t>
-        </is>
-      </c>
+      <c r="T6" s="11" t="inlineStr"/>
+      <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
@@ -18475,7 +18011,7 @@
       <c r="M7" s="12" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>8I, 8II</t>
+          <t>8I, 4II, 2I</t>
         </is>
       </c>
       <c r="O7" s="12" t="inlineStr"/>
@@ -18483,16 +18019,8 @@
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr">
-        <is>
-          <t>4II, 2I</t>
-        </is>
-      </c>
-      <c r="U7" s="12" t="inlineStr">
-        <is>
-          <t>D3, D1</t>
-        </is>
-      </c>
+      <c r="T7" s="11" t="inlineStr"/>
+      <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
@@ -18553,18 +18081,14 @@
           <t>6</t>
         </is>
       </c>
-      <c r="O8" s="12" t="inlineStr">
-        <is>
-          <t>2I, 8II</t>
-        </is>
-      </c>
+      <c r="O8" s="12" t="inlineStr"/>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr"/>
       <c r="S8" s="12" t="inlineStr"/>
       <c r="T8" s="11" t="inlineStr">
         <is>
-          <t>2I, 2I</t>
+          <t>2I</t>
         </is>
       </c>
       <c r="U8" s="12" t="inlineStr">
@@ -18572,11 +18096,7 @@
           <t>A2, D1</t>
         </is>
       </c>
-      <c r="V8" s="11" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
+      <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
       <c r="X8" s="11" t="inlineStr"/>
       <c r="Y8" s="12" t="inlineStr"/>
@@ -18632,18 +18152,14 @@
           <t>8II</t>
         </is>
       </c>
-      <c r="O9" s="12" t="inlineStr">
-        <is>
-          <t>2I, 8II</t>
-        </is>
-      </c>
+      <c r="O9" s="12" t="inlineStr"/>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
       <c r="T9" s="11" t="inlineStr">
         <is>
-          <t>2I, 2I</t>
+          <t>2I</t>
         </is>
       </c>
       <c r="U9" s="12" t="inlineStr">
@@ -18651,11 +18167,7 @@
           <t>A2, D1</t>
         </is>
       </c>
-      <c r="V9" s="11" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
+      <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
       <c r="X9" s="11" t="inlineStr"/>
       <c r="Y9" s="12" t="inlineStr"/>
@@ -21929,11 +21441,7 @@
       <c r="T6" s="11" t="inlineStr"/>
       <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
-      <c r="W6" s="12" t="inlineStr">
-        <is>
-          <t>8I</t>
-        </is>
-      </c>
+      <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
       <c r="Y6" s="12" t="inlineStr"/>
       <c r="Z6" s="11" t="inlineStr"/>
@@ -22005,11 +21513,7 @@
       <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
-      <c r="X7" s="11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="X7" s="11" t="inlineStr"/>
       <c r="Y7" s="12" t="inlineStr"/>
       <c r="Z7" s="11" t="inlineStr"/>
       <c r="AA7" s="13" t="inlineStr"/>
@@ -22188,7 +21692,7 @@
       <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="11" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>3I, 1I</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr"/>
@@ -22197,16 +21701,8 @@
       <c r="T10" s="11" t="inlineStr"/>
       <c r="U10" s="12" t="inlineStr"/>
       <c r="V10" s="11" t="inlineStr"/>
-      <c r="W10" s="12" t="inlineStr">
-        <is>
-          <t>3I, 1I</t>
-        </is>
-      </c>
-      <c r="X10" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+      <c r="W10" s="12" t="inlineStr"/>
+      <c r="X10" s="11" t="inlineStr"/>
       <c r="Y10" s="12" t="inlineStr"/>
       <c r="Z10" s="11" t="inlineStr"/>
       <c r="AA10" s="13" t="inlineStr"/>
@@ -22276,16 +21772,8 @@
       <c r="T11" s="11" t="inlineStr"/>
       <c r="U11" s="12" t="inlineStr"/>
       <c r="V11" s="11" t="inlineStr"/>
-      <c r="W11" s="12" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
-      <c r="X11" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+      <c r="W11" s="12" t="inlineStr"/>
+      <c r="X11" s="11" t="inlineStr"/>
       <c r="Y11" s="12" t="inlineStr"/>
       <c r="Z11" s="11" t="inlineStr"/>
       <c r="AA11" s="13" t="inlineStr"/>
@@ -22350,7 +21838,7 @@
       <c r="O12" s="12" t="inlineStr"/>
       <c r="P12" s="11" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>3I, 1I</t>
         </is>
       </c>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -22359,16 +21847,8 @@
       <c r="T12" s="11" t="inlineStr"/>
       <c r="U12" s="12" t="inlineStr"/>
       <c r="V12" s="11" t="inlineStr"/>
-      <c r="W12" s="12" t="inlineStr">
-        <is>
-          <t>3I, 1I</t>
-        </is>
-      </c>
-      <c r="X12" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+      <c r="W12" s="12" t="inlineStr"/>
+      <c r="X12" s="11" t="inlineStr"/>
       <c r="Y12" s="12" t="inlineStr"/>
       <c r="Z12" s="11" t="inlineStr"/>
       <c r="AA12" s="13" t="inlineStr"/>
@@ -22442,16 +21922,8 @@
       <c r="T13" s="11" t="inlineStr"/>
       <c r="U13" s="12" t="inlineStr"/>
       <c r="V13" s="11" t="inlineStr"/>
-      <c r="W13" s="12" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
-      <c r="X13" s="11" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
+      <c r="W13" s="12" t="inlineStr"/>
+      <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
       <c r="Z13" s="11" t="inlineStr"/>
       <c r="AA13" s="13" t="inlineStr"/>
@@ -22561,7 +22033,7 @@
       <c r="M15" s="12" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6, 4I</t>
         </is>
       </c>
       <c r="O15" s="12" t="inlineStr"/>
@@ -22569,11 +22041,7 @@
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr">
-        <is>
-          <t>4I</t>
-        </is>
-      </c>
+      <c r="T15" s="11" t="inlineStr"/>
       <c r="U15" s="12" t="inlineStr"/>
       <c r="V15" s="11" t="inlineStr"/>
       <c r="W15" s="12" t="inlineStr"/>
@@ -22624,7 +22092,7 @@
       <c r="M16" s="12" t="inlineStr"/>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>8II</t>
+          <t>8II, 4I</t>
         </is>
       </c>
       <c r="O16" s="12" t="inlineStr"/>
@@ -22632,11 +22100,7 @@
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr"/>
       <c r="S16" s="12" t="inlineStr"/>
-      <c r="T16" s="11" t="inlineStr">
-        <is>
-          <t>4I</t>
-        </is>
-      </c>
+      <c r="T16" s="11" t="inlineStr"/>
       <c r="U16" s="12" t="inlineStr"/>
       <c r="V16" s="11" t="inlineStr"/>
       <c r="W16" s="12" t="inlineStr"/>
@@ -22707,27 +22171,15 @@
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr"/>
       <c r="S17" s="12" t="inlineStr"/>
-      <c r="T17" s="11" t="inlineStr">
-        <is>
-          <t>2I</t>
-        </is>
-      </c>
+      <c r="T17" s="11" t="inlineStr"/>
       <c r="U17" s="12" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="V17" s="11" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
+      <c r="V17" s="11" t="inlineStr"/>
       <c r="W17" s="12" t="inlineStr"/>
-      <c r="X17" s="11" t="inlineStr">
-        <is>
-          <t>8II</t>
-        </is>
-      </c>
+      <c r="X17" s="11" t="inlineStr"/>
       <c r="Y17" s="12" t="inlineStr"/>
       <c r="Z17" s="11" t="inlineStr"/>
       <c r="AA17" s="13" t="inlineStr"/>
@@ -22790,21 +22242,13 @@
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="11" t="inlineStr"/>
       <c r="S18" s="12" t="inlineStr"/>
-      <c r="T18" s="11" t="inlineStr">
-        <is>
-          <t>2I</t>
-        </is>
-      </c>
+      <c r="T18" s="11" t="inlineStr"/>
       <c r="U18" s="12" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="V18" s="11" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
+      <c r="V18" s="11" t="inlineStr"/>
       <c r="W18" s="12" t="inlineStr"/>
       <c r="X18" s="11" t="inlineStr"/>
       <c r="Y18" s="12" t="inlineStr"/>
@@ -22861,30 +22305,22 @@
       <c r="M19" s="12" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>8II</t>
+          <t>4II</t>
         </is>
       </c>
       <c r="O19" s="12" t="inlineStr"/>
       <c r="P19" s="11" t="inlineStr"/>
-      <c r="Q19" s="12" t="inlineStr"/>
+      <c r="Q19" s="12" t="inlineStr">
+        <is>
+          <t>8II</t>
+        </is>
+      </c>
       <c r="R19" s="11" t="inlineStr"/>
       <c r="S19" s="12" t="inlineStr"/>
-      <c r="T19" s="11" t="inlineStr">
-        <is>
-          <t>4II</t>
-        </is>
-      </c>
-      <c r="U19" s="12" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="T19" s="11" t="inlineStr"/>
+      <c r="U19" s="12" t="inlineStr"/>
       <c r="V19" s="11" t="inlineStr"/>
-      <c r="W19" s="12" t="inlineStr">
-        <is>
-          <t>8II</t>
-        </is>
-      </c>
+      <c r="W19" s="12" t="inlineStr"/>
       <c r="X19" s="11" t="inlineStr"/>
       <c r="Y19" s="12" t="inlineStr"/>
       <c r="Z19" s="11" t="inlineStr"/>
@@ -22940,7 +22376,7 @@
       </c>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>8II</t>
+          <t>4II</t>
         </is>
       </c>
       <c r="O20" s="12" t="inlineStr"/>
@@ -22948,16 +22384,8 @@
       <c r="Q20" s="12" t="inlineStr"/>
       <c r="R20" s="11" t="inlineStr"/>
       <c r="S20" s="12" t="inlineStr"/>
-      <c r="T20" s="11" t="inlineStr">
-        <is>
-          <t>4II</t>
-        </is>
-      </c>
-      <c r="U20" s="12" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
+      <c r="T20" s="11" t="inlineStr"/>
+      <c r="U20" s="12" t="inlineStr"/>
       <c r="V20" s="11" t="inlineStr"/>
       <c r="W20" s="12" t="inlineStr"/>
       <c r="X20" s="11" t="inlineStr"/>
@@ -26319,7 +25747,7 @@
       </c>
       <c r="C8" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">main_ol_distance 120
+          <t xml:space="preserve">main_ol_distance 150
 </t>
         </is>
       </c>

--- a/stations/output/SPE_Interlocking_Program.xlsx
+++ b/stations/output/SPE_Interlocking_Program.xlsx
@@ -1757,7 +1757,7 @@
       </c>
       <c r="S6" s="12" t="inlineStr">
         <is>
-          <t>6, A2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="T6" s="11" t="inlineStr"/>
@@ -1883,11 +1883,7 @@
           <t>8II</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="M8" s="12" t="inlineStr"/>
       <c r="N8" s="11" t="inlineStr">
         <is>
           <t>3I</t>
@@ -1968,7 +1964,7 @@
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr">
         <is>
-          <t>8II, 8I</t>
+          <t>8II</t>
         </is>
       </c>
       <c r="N9" s="11" t="inlineStr">
@@ -2464,7 +2460,7 @@
       </c>
       <c r="S15" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 1I</t>
+          <t>1II/3II</t>
         </is>
       </c>
       <c r="T15" s="11" t="inlineStr"/>
@@ -2551,7 +2547,7 @@
       </c>
       <c r="S16" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 3I, D4</t>
+          <t>1II/3II, 3I</t>
         </is>
       </c>
       <c r="T16" s="11" t="inlineStr"/>
@@ -2733,7 +2729,7 @@
       </c>
       <c r="S18" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 1I</t>
+          <t>1II/3II</t>
         </is>
       </c>
       <c r="T18" s="11" t="inlineStr"/>
@@ -2824,7 +2820,7 @@
       </c>
       <c r="S19" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 3I, D4</t>
+          <t>1II/3II, 3I</t>
         </is>
       </c>
       <c r="T19" s="11" t="inlineStr"/>
@@ -3206,11 +3202,7 @@
           <t>2I, 2II</t>
         </is>
       </c>
-      <c r="L24" s="11" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="L24" s="11" t="inlineStr"/>
       <c r="M24" s="12" t="inlineStr"/>
       <c r="N24" s="11" t="inlineStr">
         <is>
@@ -3231,7 +3223,7 @@
       </c>
       <c r="S24" s="12" t="inlineStr">
         <is>
-          <t>1I, A1</t>
+          <t>1I</t>
         </is>
       </c>
       <c r="T24" s="11" t="inlineStr">
@@ -9821,11 +9813,7 @@
           <t>8II</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="M6" s="12" t="inlineStr"/>
       <c r="N6" s="11" t="inlineStr">
         <is>
           <t>1I</t>
@@ -9902,7 +9890,7 @@
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr">
         <is>
-          <t>8II, 8I</t>
+          <t>8II</t>
         </is>
       </c>
       <c r="N7" s="11" t="inlineStr">
@@ -10141,7 +10129,7 @@
       </c>
       <c r="S10" s="12" t="inlineStr">
         <is>
-          <t>8I, D3</t>
+          <t>8I</t>
         </is>
       </c>
       <c r="T10" s="11" t="inlineStr"/>
@@ -10544,7 +10532,7 @@
       </c>
       <c r="S15" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 1I</t>
+          <t>1II/3II</t>
         </is>
       </c>
       <c r="T15" s="11" t="inlineStr"/>
@@ -10631,7 +10619,7 @@
       </c>
       <c r="S16" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 3I, D4</t>
+          <t>1II/3II, 3I</t>
         </is>
       </c>
       <c r="T16" s="11" t="inlineStr"/>
@@ -10817,7 +10805,7 @@
       </c>
       <c r="S18" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 1I</t>
+          <t>1II/3II</t>
         </is>
       </c>
       <c r="T18" s="11" t="inlineStr">
@@ -10912,7 +10900,7 @@
       </c>
       <c r="S19" s="12" t="inlineStr">
         <is>
-          <t>1II/3II, 3I, D4</t>
+          <t>1II/3II, 3I</t>
         </is>
       </c>
       <c r="T19" s="11" t="inlineStr">
@@ -11302,11 +11290,7 @@
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr"/>
-      <c r="L24" s="11" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="L24" s="11" t="inlineStr"/>
       <c r="M24" s="12" t="inlineStr"/>
       <c r="N24" s="11" t="inlineStr">
         <is>
@@ -11327,7 +11311,7 @@
       </c>
       <c r="S24" s="12" t="inlineStr">
         <is>
-          <t>1I, A1</t>
+          <t>1I</t>
         </is>
       </c>
       <c r="T24" s="11" t="inlineStr">
@@ -25747,7 +25731,7 @@
       </c>
       <c r="C8" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">main_ol_distance 150
+          <t xml:space="preserve">main_ol_distance 120
 </t>
         </is>
       </c>

--- a/stations/output/SPE_Interlocking_Program.xlsx
+++ b/stations/output/SPE_Interlocking_Program.xlsx
@@ -1206,7 +1206,7 @@
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v1.0.0</t>
+          <t>v1.0.1</t>
         </is>
       </c>
     </row>

--- a/stations/output/SPE_Interlocking_Program.xlsx
+++ b/stations/output/SPE_Interlocking_Program.xlsx
@@ -25556,7 +25556,7 @@
       </c>
       <c r="C1" s="36" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Operational Parameters</t>
         </is>
       </c>
       <c r="D1" s="37" t="inlineStr">

--- a/stations/output/SPE_Interlocking_Program.xlsx
+++ b/stations/output/SPE_Interlocking_Program.xlsx
@@ -462,15 +462,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color theme="1"/>
@@ -479,37 +470,6 @@
         <color theme="1"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -531,30 +491,6 @@
       <top style="thin">
         <color theme="1"/>
       </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
@@ -585,6 +521,39 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color theme="1"/>
@@ -592,6 +561,15 @@
       <top style="medium">
         <color theme="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -609,6 +587,17 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color theme="1"/>
@@ -639,12 +628,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -788,9 +788,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -818,29 +815,42 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1183,49 +1193,49 @@
       <c r="B1" s="21" t="n"/>
       <c r="C1" s="21" t="n"/>
       <c r="D1" s="21" t="n"/>
-      <c r="E1" s="59" t="inlineStr">
+      <c r="E1" s="61" t="inlineStr">
         <is>
           <t>ZIRCON</t>
         </is>
       </c>
-      <c r="F1" s="60" t="n"/>
+      <c r="F1" s="62" t="n"/>
     </row>
     <row r="2" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A2" s="22" t="n"/>
-      <c r="B2" s="49" t="n"/>
-      <c r="C2" s="49" t="n"/>
-      <c r="D2" s="49" t="n"/>
-      <c r="E2" s="61" t="n"/>
-      <c r="F2" s="62" t="n"/>
+      <c r="A2" s="58" t="n"/>
+      <c r="B2" s="59" t="n"/>
+      <c r="C2" s="59" t="n"/>
+      <c r="D2" s="59" t="n"/>
+      <c r="E2" s="63" t="n"/>
+      <c r="F2" s="64" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="n"/>
-      <c r="B3" s="49" t="n"/>
-      <c r="C3" s="49" t="n"/>
-      <c r="D3" s="49" t="n"/>
-      <c r="E3" s="49" t="n"/>
+      <c r="A3" s="58" t="n"/>
+      <c r="B3" s="59" t="n"/>
+      <c r="C3" s="59" t="n"/>
+      <c r="D3" s="59" t="n"/>
+      <c r="E3" s="59" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v1.0.1</t>
+          <t>v1.0.2</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="n"/>
-      <c r="B4" s="49" t="n"/>
-      <c r="C4" s="49" t="n"/>
-      <c r="D4" s="49" t="n"/>
-      <c r="E4" s="49" t="n"/>
-      <c r="F4" s="23" t="n"/>
+      <c r="A4" s="58" t="n"/>
+      <c r="B4" s="59" t="n"/>
+      <c r="C4" s="59" t="n"/>
+      <c r="D4" s="59" t="n"/>
+      <c r="E4" s="59" t="n"/>
+      <c r="F4" s="60" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="n"/>
+      <c r="A5" s="58" t="n"/>
       <c r="B5" s="48" t="inlineStr">
         <is>
           <t>Interlocking Program</t>
         </is>
       </c>
-      <c r="F5" s="23" t="n"/>
+      <c r="F5" s="60" t="n"/>
     </row>
     <row r="6" ht="14.4" customHeight="1">
       <c r="A6" s="24" t="n"/>
@@ -1240,94 +1250,92 @@
       <c r="F7" s="25" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="49" t="inlineStr">
-        <is>
-          <t>São Pedro do Estoril (SPE)</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="n"/>
+      <c r="A8" s="65" t="inlineStr">
+        <is>
+          <t>São Pedro do Estoril (NOT REAL DATA - FOR TESTING ONLY) (SPE)</t>
+        </is>
+      </c>
+      <c r="F8" s="66" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="49" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>Linha de Cascais</t>
         </is>
       </c>
-      <c r="F9" s="23" t="n"/>
+      <c r="F9" s="66" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="49" t="n"/>
-      <c r="C10" s="49" t="n"/>
-      <c r="D10" s="49" t="n"/>
-      <c r="E10" s="49" t="n"/>
-      <c r="F10" s="23" t="n"/>
+      <c r="A10" s="58" t="n"/>
+      <c r="B10" s="59" t="n"/>
+      <c r="C10" s="59" t="n"/>
+      <c r="D10" s="59" t="n"/>
+      <c r="E10" s="59" t="n"/>
+      <c r="F10" s="60" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n"/>
-      <c r="B11" s="49" t="n"/>
-      <c r="C11" s="49" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="23" t="n"/>
+      <c r="A11" s="58" t="n"/>
+      <c r="B11" s="59" t="n"/>
+      <c r="C11" s="59" t="n"/>
+      <c r="D11" s="59" t="n"/>
+      <c r="E11" s="59" t="n"/>
+      <c r="F11" s="60" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="49" t="n"/>
-      <c r="C12" s="49" t="n"/>
-      <c r="D12" s="49" t="n"/>
-      <c r="E12" s="49" t="n"/>
-      <c r="F12" s="23" t="n"/>
+      <c r="A12" s="58" t="n"/>
+      <c r="B12" s="59" t="n"/>
+      <c r="C12" s="59" t="n"/>
+      <c r="D12" s="59" t="n"/>
+      <c r="E12" s="59" t="n"/>
+      <c r="F12" s="60" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="n"/>
-      <c r="B13" s="49" t="n"/>
-      <c r="C13" s="49" t="n"/>
-      <c r="D13" s="49" t="n"/>
-      <c r="E13" s="49" t="n"/>
-      <c r="F13" s="23" t="n"/>
+      <c r="A13" s="58" t="n"/>
+      <c r="B13" s="59" t="n"/>
+      <c r="C13" s="59" t="n"/>
+      <c r="D13" s="59" t="n"/>
+      <c r="E13" s="59" t="n"/>
+      <c r="F13" s="60" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="49" t="n"/>
-      <c r="C14" s="49" t="n"/>
-      <c r="D14" s="49" t="n"/>
-      <c r="E14" s="49" t="n"/>
-      <c r="F14" s="23" t="n"/>
+      <c r="A14" s="58" t="n"/>
+      <c r="B14" s="59" t="n"/>
+      <c r="C14" s="59" t="n"/>
+      <c r="D14" s="59" t="n"/>
+      <c r="E14" s="59" t="n"/>
+      <c r="F14" s="60" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n"/>
-      <c r="B15" s="49" t="n"/>
-      <c r="C15" s="49" t="n"/>
-      <c r="D15" s="49" t="n"/>
-      <c r="E15" s="49" t="n"/>
-      <c r="F15" s="23" t="n"/>
+      <c r="A15" s="58" t="n"/>
+      <c r="B15" s="59" t="n"/>
+      <c r="C15" s="59" t="n"/>
+      <c r="D15" s="59" t="n"/>
+      <c r="E15" s="59" t="n"/>
+      <c r="F15" s="60" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="49" t="n"/>
-      <c r="C16" s="49" t="n"/>
-      <c r="D16" s="49" t="n"/>
-      <c r="E16" s="49" t="n"/>
-      <c r="F16" s="23" t="n"/>
+      <c r="A16" s="58" t="n"/>
+      <c r="B16" s="59" t="n"/>
+      <c r="C16" s="59" t="n"/>
+      <c r="D16" s="59" t="n"/>
+      <c r="E16" s="59" t="n"/>
+      <c r="F16" s="60" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="n"/>
-      <c r="B17" s="49" t="n"/>
-      <c r="C17" s="49" t="n"/>
-      <c r="D17" s="49" t="n"/>
-      <c r="E17" s="49" t="n"/>
-      <c r="F17" s="23" t="n"/>
+      <c r="A17" s="58" t="n"/>
+      <c r="B17" s="59" t="n"/>
+      <c r="C17" s="59" t="n"/>
+      <c r="D17" s="59" t="n"/>
+      <c r="E17" s="59" t="n"/>
+      <c r="F17" s="60" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="49" t="n"/>
-      <c r="C18" s="49" t="n"/>
-      <c r="D18" s="49" t="n"/>
-      <c r="E18" s="49" t="n"/>
-      <c r="F18" s="23" t="n"/>
+      <c r="A18" s="58" t="n"/>
+      <c r="B18" s="59" t="n"/>
+      <c r="C18" s="59" t="n"/>
+      <c r="D18" s="59" t="n"/>
+      <c r="E18" s="59" t="n"/>
+      <c r="F18" s="60" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="30" t="inlineStr">
@@ -1335,11 +1343,11 @@
           <t>Diogo Luís</t>
         </is>
       </c>
-      <c r="B19" s="49" t="n"/>
-      <c r="C19" s="49" t="n"/>
-      <c r="D19" s="49" t="n"/>
-      <c r="E19" s="49" t="n"/>
-      <c r="F19" s="23" t="n"/>
+      <c r="B19" s="59" t="n"/>
+      <c r="C19" s="59" t="n"/>
+      <c r="D19" s="59" t="n"/>
+      <c r="E19" s="59" t="n"/>
+      <c r="F19" s="60" t="n"/>
     </row>
     <row r="20" ht="16.2" customHeight="1" thickBot="1">
       <c r="A20" s="31" t="inlineStr">
@@ -1355,9 +1363,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="B5:E6"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A9:F9"/>
     <mergeCell ref="E1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1385,310 +1393,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -2206,12 +2214,12 @@
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr">
         <is>
-          <t>D1, 2I, 4II, D3, 8I, II</t>
+          <t>B1, 2I, 4II, B3, 8I, II</t>
         </is>
       </c>
       <c r="S12" s="12" t="inlineStr">
         <is>
-          <t>3I, D4</t>
+          <t>3I, B4</t>
         </is>
       </c>
       <c r="T12" s="11" t="inlineStr"/>
@@ -2364,7 +2372,7 @@
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>D1, 2I, 4II, D3, 8I, 8II, III</t>
+          <t>B1, 2I, 4II, B3, 8I, 8II, III</t>
         </is>
       </c>
       <c r="S14" s="12" t="inlineStr">
@@ -2455,7 +2463,7 @@
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr">
         <is>
-          <t>D1, 2I, 4II, D3, 8I, 8II, III</t>
+          <t>B1, 2I, 4II, B3, 8I, 8II, III</t>
         </is>
       </c>
       <c r="S15" s="12" t="inlineStr">
@@ -2542,7 +2550,7 @@
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr">
         <is>
-          <t>D1, 2I, 4II, D3, 8I, 8II, III</t>
+          <t>B1, 2I, 4II, B3, 8I, 8II, III</t>
         </is>
       </c>
       <c r="S16" s="12" t="inlineStr">
@@ -2629,7 +2637,7 @@
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>D1, 2I, 2II, 4I, A2, 6, 8II, III</t>
+          <t>B1, 2I, 2II, 4I, A2, 6, 8II, III</t>
         </is>
       </c>
       <c r="S17" s="12" t="inlineStr">
@@ -2724,7 +2732,7 @@
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t>D1, 2I, 2II, 4I, A2, 6, 8II, III</t>
+          <t>B1, 2I, 2II, 4I, A2, 6, 8II, III</t>
         </is>
       </c>
       <c r="S18" s="12" t="inlineStr">
@@ -2815,7 +2823,7 @@
       <c r="Q19" s="12" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>D1, 2I, 2II, 4I, A2, 6, 8II, III</t>
+          <t>B1, 2I, 2II, 4I, A2, 6, 8II, III</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr">
@@ -3218,7 +3226,7 @@
       <c r="Q24" s="12" t="inlineStr"/>
       <c r="R24" s="11" t="inlineStr">
         <is>
-          <t>D1, 2I, 2II, 4I, A2, 6, I</t>
+          <t>B1, 2I, 2II, 4I, A2, 6, I</t>
         </is>
       </c>
       <c r="S24" s="12" t="inlineStr">
@@ -5687,310 +5695,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -6267,7 +6275,7 @@
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr">
         <is>
-          <t>8II, 8I, D3, 4II, 4I, 2II, A3</t>
+          <t>8II, 8I, B3, 4II, 4I, 2II, A3</t>
         </is>
       </c>
       <c r="S9" s="12" t="inlineStr"/>
@@ -6278,7 +6286,7 @@
       </c>
       <c r="U9" s="12" t="inlineStr">
         <is>
-          <t>A2, D1</t>
+          <t>A2, B1</t>
         </is>
       </c>
       <c r="V9" s="11" t="inlineStr"/>
@@ -6428,7 +6436,7 @@
       </c>
       <c r="U11" s="12" t="inlineStr">
         <is>
-          <t>A2, D1</t>
+          <t>A2, B1</t>
         </is>
       </c>
       <c r="V11" s="11" t="inlineStr"/>
@@ -6496,7 +6504,7 @@
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr">
         <is>
-          <t>8I, D3, 4II, 4I, 2II, A3</t>
+          <t>8I, B3, 4II, 4I, 2II, A3</t>
         </is>
       </c>
       <c r="S12" s="12" t="inlineStr"/>
@@ -6507,7 +6515,7 @@
       </c>
       <c r="U12" s="12" t="inlineStr">
         <is>
-          <t>A2, D1</t>
+          <t>A2, B1</t>
         </is>
       </c>
       <c r="V12" s="11" t="inlineStr"/>
@@ -6582,7 +6590,7 @@
       </c>
       <c r="U13" s="12" t="inlineStr">
         <is>
-          <t>A2, D1</t>
+          <t>A2, B1</t>
         </is>
       </c>
       <c r="V13" s="11" t="inlineStr"/>
@@ -6646,7 +6654,7 @@
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>3I, D4</t>
+          <t>3I, B4</t>
         </is>
       </c>
       <c r="S14" s="12" t="inlineStr"/>
@@ -6776,7 +6784,7 @@
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr">
         <is>
-          <t>1II/3II, 3I, D4</t>
+          <t>1II/3II, 3I, B4</t>
         </is>
       </c>
       <c r="S16" s="12" t="inlineStr"/>
@@ -9457,310 +9465,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -9828,7 +9836,7 @@
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr">
         <is>
-          <t>D4, 3I, 1II/3II, III</t>
+          <t>B4, 3I, 1II/3II, III</t>
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr">
@@ -9907,7 +9915,7 @@
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr">
         <is>
-          <t>D4, 3I, 1II/3II, III</t>
+          <t>B4, 3I, 1II/3II, III</t>
         </is>
       </c>
       <c r="S7" s="12" t="inlineStr">
@@ -10124,7 +10132,7 @@
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr">
         <is>
-          <t>D4, 3I, II</t>
+          <t>B4, 3I, II</t>
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr">
@@ -10266,12 +10274,12 @@
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr">
         <is>
-          <t>A3, 2II, 4I, 4II, D3, 8I, II</t>
+          <t>A3, 2II, 4I, 4II, B3, 8I, II</t>
         </is>
       </c>
       <c r="S12" s="12" t="inlineStr">
         <is>
-          <t>3I, D4</t>
+          <t>3I, B4</t>
         </is>
       </c>
       <c r="T12" s="11" t="inlineStr">
@@ -10281,7 +10289,7 @@
       </c>
       <c r="U12" s="12" t="inlineStr">
         <is>
-          <t>D1, A2, 8II</t>
+          <t>B1, A2, 8II</t>
         </is>
       </c>
       <c r="V12" s="11" t="inlineStr"/>
@@ -10356,7 +10364,7 @@
       </c>
       <c r="U13" s="12" t="inlineStr">
         <is>
-          <t>D1, A2, 8II</t>
+          <t>B1, A2, 8II</t>
         </is>
       </c>
       <c r="V13" s="11" t="inlineStr"/>
@@ -10701,7 +10709,7 @@
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>A3, 2II, 4I, 4II, D3, 8I, 8II, III</t>
+          <t>A3, 2II, 4I, 4II, B3, 8I, 8II, III</t>
         </is>
       </c>
       <c r="S17" s="12" t="inlineStr">
@@ -10716,7 +10724,7 @@
       </c>
       <c r="U17" s="12" t="inlineStr">
         <is>
-          <t>D1, A2</t>
+          <t>B1, A2</t>
         </is>
       </c>
       <c r="V17" s="11" t="inlineStr"/>
@@ -10800,7 +10808,7 @@
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t>A3, 2II, 4I, 4II, D3, 8I, 8II, III</t>
+          <t>A3, 2II, 4I, 4II, B3, 8I, 8II, III</t>
         </is>
       </c>
       <c r="S18" s="12" t="inlineStr">
@@ -10815,7 +10823,7 @@
       </c>
       <c r="U18" s="12" t="inlineStr">
         <is>
-          <t>D1, A2</t>
+          <t>B1, A2</t>
         </is>
       </c>
       <c r="V18" s="11" t="inlineStr"/>
@@ -10895,7 +10903,7 @@
       <c r="Q19" s="12" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>A3, 2II, 4I, 4II, D3, 8I, 8II, III</t>
+          <t>A3, 2II, 4I, 4II, B3, 8I, 8II, III</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr">
@@ -10910,7 +10918,7 @@
       </c>
       <c r="U19" s="12" t="inlineStr">
         <is>
-          <t>D1, A2</t>
+          <t>B1, A2</t>
         </is>
       </c>
       <c r="V19" s="11" t="inlineStr"/>
@@ -11155,7 +11163,7 @@
       </c>
       <c r="U22" s="12" t="inlineStr">
         <is>
-          <t>D1, A2</t>
+          <t>B1, A2</t>
         </is>
       </c>
       <c r="V22" s="11" t="inlineStr"/>
@@ -11242,7 +11250,7 @@
       </c>
       <c r="U23" s="12" t="inlineStr">
         <is>
-          <t>D1, A2</t>
+          <t>B1, A2</t>
         </is>
       </c>
       <c r="V23" s="11" t="inlineStr"/>
@@ -13763,310 +13771,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -14134,7 +14142,7 @@
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr">
         <is>
-          <t>6, A2, 4I, 2II, 2I, D1</t>
+          <t>6, A2, 4I, 2II, 2I, B1</t>
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
@@ -14296,7 +14304,7 @@
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr">
         <is>
-          <t>8II, 6, A2, 4I, 2II, 2I, D1</t>
+          <t>8II, 6, A2, 4I, 2II, 2I, B1</t>
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr"/>
@@ -14379,7 +14387,7 @@
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr">
         <is>
-          <t>8II, 8I, D3, 4II, 2I, D1</t>
+          <t>8II, 8I, B3, 4II, 2I, B1</t>
         </is>
       </c>
       <c r="S9" s="12" t="inlineStr"/>
@@ -14604,7 +14612,7 @@
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr">
         <is>
-          <t>8I, D3, 4II, 2I, D1</t>
+          <t>8I, B3, 4II, 2I, B1</t>
         </is>
       </c>
       <c r="S12" s="12" t="inlineStr"/>
@@ -17573,310 +17581,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -18077,7 +18085,7 @@
       </c>
       <c r="U8" s="12" t="inlineStr">
         <is>
-          <t>A2, D1</t>
+          <t>A2, B1</t>
         </is>
       </c>
       <c r="V8" s="11" t="inlineStr"/>
@@ -18148,7 +18156,7 @@
       </c>
       <c r="U9" s="12" t="inlineStr">
         <is>
-          <t>A2, D1</t>
+          <t>A2, B1</t>
         </is>
       </c>
       <c r="V9" s="11" t="inlineStr"/>
@@ -18179,7 +18187,7 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -18238,7 +18246,7 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
@@ -21051,310 +21059,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -21371,7 +21379,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -21442,7 +21450,7 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -21513,7 +21521,7 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -21572,7 +21580,7 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -21631,7 +21639,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -21702,7 +21710,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -21768,7 +21776,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M80</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -21843,7 +21851,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M80</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -21918,7 +21926,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M80</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -22114,7 +22122,7 @@
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
@@ -22189,7 +22197,7 @@
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
@@ -22255,7 +22263,7 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M80</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
@@ -22326,7 +22334,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M80</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
@@ -24884,24 +24892,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="B1" s="66" t="n"/>
-      <c r="C1" s="55" t="inlineStr">
+      <c r="B1" s="70" t="n"/>
+      <c r="C1" s="54" t="inlineStr">
         <is>
           <t>Approach Route Cancel</t>
         </is>
       </c>
-      <c r="D1" s="66" t="n"/>
-      <c r="E1" s="55" t="inlineStr">
+      <c r="D1" s="70" t="n"/>
+      <c r="E1" s="54" t="inlineStr">
         <is>
           <t>Emergency Route Cancel</t>
         </is>
       </c>
-      <c r="F1" s="66" t="n"/>
+      <c r="F1" s="70" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -24909,27 +24917,27 @@
           <t>Track</t>
         </is>
       </c>
-      <c r="B2" s="50" t="inlineStr">
+      <c r="B2" s="49" t="inlineStr">
         <is>
           <t>Delay [s]</t>
         </is>
       </c>
-      <c r="C2" s="50" t="inlineStr">
+      <c r="C2" s="49" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="D2" s="50" t="inlineStr">
+      <c r="D2" s="49" t="inlineStr">
         <is>
           <t>Delay [s]</t>
         </is>
       </c>
-      <c r="E2" s="50" t="inlineStr">
+      <c r="E2" s="49" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="F2" s="57" t="inlineStr">
+      <c r="F2" s="56" t="inlineStr">
         <is>
           <t>Delay [s]</t>
         </is>
@@ -25042,7 +25050,7 @@
     <row r="7">
       <c r="A7" s="32" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
@@ -25178,7 +25186,7 @@
       <c r="D13" s="12" t="n"/>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>M80</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
@@ -25192,7 +25200,7 @@
       <c r="D14" s="12" t="n"/>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
@@ -25586,7 +25594,7 @@
       </c>
       <c r="D2" s="40" t="inlineStr">
         <is>
-          <t xml:space="preserve">station_name São Pedro do Estoril
+          <t xml:space="preserve">station_name São Pedro do Estoril (NOT REAL DATA - FOR TESTING ONLY)
 </t>
         </is>
       </c>
@@ -25600,7 +25608,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    A1 20727 20580
+          <t xml:space="preserve">    A1 120727 120580
 </t>
         </is>
       </c>
@@ -25626,7 +25634,7 @@
       </c>
       <c r="B4" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    D4 20813 20580
+          <t xml:space="preserve">    B4 120813 120580
 </t>
         </is>
       </c>
@@ -25652,7 +25660,7 @@
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1I 20870 20815 20727
+          <t xml:space="preserve">    1I 120870 120815 120727
 </t>
         </is>
       </c>
@@ -25678,7 +25686,7 @@
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1II/3II 20935 20880 20760 20815
+          <t xml:space="preserve">    1II/3II 120935 120880 120760 120815
 </t>
         </is>
       </c>
@@ -25704,7 +25712,7 @@
       </c>
       <c r="B7" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3I 20880 20904 20813
+          <t xml:space="preserve">    3I 120880 120904 120813
 </t>
         </is>
       </c>
@@ -25725,7 +25733,7 @@
       </c>
       <c r="B8" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    I 21164 20870
+          <t xml:space="preserve">    I 121164 120870
 </t>
         </is>
       </c>
@@ -25740,13 +25748,13 @@
     <row r="9">
       <c r="A9" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEC D4
+          <t xml:space="preserve">SEC B4
 </t>
         </is>
       </c>
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    III 21127 20935
+          <t xml:space="preserve">    III 121127 120935
 </t>
         </is>
       </c>
@@ -25767,7 +25775,7 @@
       </c>
       <c r="B10" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    II 21151 20904
+          <t xml:space="preserve">    II 121151 120904
 </t>
         </is>
       </c>
@@ -25788,7 +25796,7 @@
       </c>
       <c r="B11" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    6 21285 21213 21164
+          <t xml:space="preserve">    6 121285 121213 121164
 </t>
         </is>
       </c>
@@ -25809,7 +25817,7 @@
       </c>
       <c r="B12" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    8II 21213 21167 21127
+          <t xml:space="preserve">    8II 121213 121167 121127
 </t>
         </is>
       </c>
@@ -25830,7 +25838,7 @@
       </c>
       <c r="B13" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    8I 21275 21151 21167
+          <t xml:space="preserve">    8I 121275 121151 121167
 </t>
         </is>
       </c>
@@ -25851,7 +25859,7 @@
       </c>
       <c r="B14" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    A2 21470 21285
+          <t xml:space="preserve">    A2 121470 121285
 </t>
         </is>
       </c>
@@ -25872,7 +25880,7 @@
       </c>
       <c r="B15" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    D3 21465 21275
+          <t xml:space="preserve">    B3 121465 121275
 </t>
         </is>
       </c>
@@ -25893,7 +25901,7 @@
       </c>
       <c r="B16" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    4I 21579 21529 21470
+          <t xml:space="preserve">    4I 121579 121529 121470
 </t>
         </is>
       </c>
@@ -25914,7 +25922,7 @@
       </c>
       <c r="B17" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    4II 21529 21579 21465
+          <t xml:space="preserve">    4II 121529 121579 121465
 </t>
         </is>
       </c>
@@ -25934,7 +25942,7 @@
       </c>
       <c r="B18" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2II 21693 21629 21579
+          <t xml:space="preserve">    2II 121693 121629 121579
 </t>
         </is>
       </c>
@@ -25954,7 +25962,7 @@
       </c>
       <c r="B19" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2I 21693 21579 21629
+          <t xml:space="preserve">    2I 121693 121579 121629
 </t>
         </is>
       </c>
@@ -25974,7 +25982,7 @@
       </c>
       <c r="B20" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    A3 21850 21693
+          <t xml:space="preserve">    A3 121850 121693
 </t>
         </is>
       </c>
@@ -25994,7 +26002,7 @@
       </c>
       <c r="B21" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    D1 21850 21693
+          <t xml:space="preserve">    B1 121850 121693
 </t>
         </is>
       </c>
@@ -26034,7 +26042,7 @@
       </c>
       <c r="B23" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1I 20747 20816
+          <t xml:space="preserve">    1I 120747 120816
 </t>
         </is>
       </c>
@@ -26054,7 +26062,7 @@
       </c>
       <c r="B24" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1II 20835 20755
+          <t xml:space="preserve">    1II 120835 120755
 </t>
         </is>
       </c>
@@ -26074,7 +26082,7 @@
       </c>
       <c r="B25" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2I 21673 21585
+          <t xml:space="preserve">    2I 121673 121585
 </t>
         </is>
       </c>
@@ -26094,7 +26102,7 @@
       </c>
       <c r="B26" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2II 21585 21673
+          <t xml:space="preserve">    2II 121585 121673
 </t>
         </is>
       </c>
@@ -26114,7 +26122,7 @@
       </c>
       <c r="B27" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3I 20839 20889
+          <t xml:space="preserve">    3I 120839 120889
 </t>
         </is>
       </c>
@@ -26134,7 +26142,7 @@
       </c>
       <c r="B28" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3II 20921 20860
+          <t xml:space="preserve">    3II 120921 120860
 </t>
         </is>
       </c>
@@ -26154,7 +26162,7 @@
       </c>
       <c r="B29" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    4I 21573 21485
+          <t xml:space="preserve">    4I 121573 121485
 </t>
         </is>
       </c>
@@ -26174,7 +26182,7 @@
       </c>
       <c r="B30" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    4II 21485 21573
+          <t xml:space="preserve">    4II 121485 121573
 </t>
         </is>
       </c>
@@ -26189,7 +26197,7 @@
       </c>
       <c r="B31" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    6 21265 21214
+          <t xml:space="preserve">    6 121265 121214
 </t>
         </is>
       </c>
@@ -26198,13 +26206,13 @@
     <row r="32">
       <c r="A32" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE C D4
+          <t xml:space="preserve">    NDE C B4
 </t>
         </is>
       </c>
       <c r="B32" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    8I 21255 21203
+          <t xml:space="preserve">    8I 121255 121203
 </t>
         </is>
       </c>
@@ -26218,7 +26226,7 @@
       </c>
       <c r="B33" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    8II 21149 21202
+          <t xml:space="preserve">    8II 121149 121202
 </t>
         </is>
       </c>
@@ -26246,7 +26254,7 @@
       </c>
       <c r="B35" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S1 20572 19648 350
+          <t xml:space="preserve">    S1 120572 119648 350
 </t>
         </is>
       </c>
@@ -26260,7 +26268,7 @@
       </c>
       <c r="B36" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SC1 20572 19759 350
+          <t xml:space="preserve">    SC1 120572 119759 350
 </t>
         </is>
       </c>
@@ -26274,7 +26282,7 @@
       </c>
       <c r="B37" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M_COS2 20605
+          <t xml:space="preserve">    M_COS2 120605
 </t>
         </is>
       </c>
@@ -26288,7 +26296,7 @@
       </c>
       <c r="B38" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M1 20813
+          <t xml:space="preserve">    M1 120813
 </t>
         </is>
       </c>
@@ -26302,7 +26310,7 @@
       </c>
       <c r="B39" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SC4 20875 23471 350
+          <t xml:space="preserve">    SC4 120875 123471 350
 </t>
         </is>
       </c>
@@ -26316,7 +26324,7 @@
       </c>
       <c r="B40" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S6/M6 20940 23471 350
+          <t xml:space="preserve">    S6/M6 120940 123471 350
 </t>
         </is>
       </c>
@@ -26330,7 +26338,7 @@
       </c>
       <c r="B41" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S4/M4 20909 23471 350
+          <t xml:space="preserve">    S4/M4 120909 123471 350
 </t>
         </is>
       </c>
@@ -26344,7 +26352,7 @@
       </c>
       <c r="B42" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S5/M5 21122 19648 350
+          <t xml:space="preserve">    S5/M5 121122 119648 350
 </t>
         </is>
       </c>
@@ -26358,7 +26366,7 @@
       </c>
       <c r="B43" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S7/M7 21146 19759 350
+          <t xml:space="preserve">    S7/M7 121146 119759 350
 </t>
         </is>
       </c>
@@ -26372,7 +26380,7 @@
       </c>
       <c r="B44" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S3/M3 21159 19648 350
+          <t xml:space="preserve">    S3/M3 121159 119648 350
 </t>
         </is>
       </c>
@@ -26380,13 +26388,13 @@
     <row r="45">
       <c r="A45" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">        SIG M8
+          <t xml:space="preserve">        SIG M80
 </t>
         </is>
       </c>
       <c r="B45" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M8 21286
+          <t xml:space="preserve">    M80 121286
 </t>
         </is>
       </c>
@@ -26400,7 +26408,7 @@
       </c>
       <c r="B46" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M10 21276
+          <t xml:space="preserve">    M10 121276
 </t>
         </is>
       </c>
@@ -26414,7 +26422,7 @@
       </c>
       <c r="B47" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M_2I 21579
+          <t xml:space="preserve">    M_2I 121579
 </t>
         </is>
       </c>
@@ -26428,7 +26436,7 @@
       </c>
       <c r="B48" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M2 21580
+          <t xml:space="preserve">    M2 121580
 </t>
         </is>
       </c>
@@ -26442,7 +26450,7 @@
       </c>
       <c r="B49" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M_CIS1 21779
+          <t xml:space="preserve">    M_CIS1 121779
 </t>
         </is>
       </c>
@@ -26456,7 +26464,7 @@
       </c>
       <c r="B50" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S2 21858 23471 350
+          <t xml:space="preserve">    S2 121858 123471 350
 </t>
         </is>
       </c>
@@ -26470,7 +26478,7 @@
       </c>
       <c r="B51" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SC2 21858 23471 350
+          <t xml:space="preserve">    SC2 121858 123471 350
 </t>
         </is>
       </c>
@@ -26523,7 +26531,7 @@
     <row r="57">
       <c r="A57" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE A D3
+          <t xml:space="preserve">    NDE A B3
 </t>
         </is>
       </c>
@@ -26604,7 +26612,7 @@
     <row r="66">
       <c r="A66" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEC D3
+          <t xml:space="preserve">SEC B3
 </t>
         </is>
       </c>
@@ -26721,7 +26729,7 @@
     <row r="79">
       <c r="A79" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE C D3
+          <t xml:space="preserve">    NDE C B3
 </t>
         </is>
       </c>
@@ -26784,7 +26792,7 @@
     <row r="86">
       <c r="A86" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE A D1
+          <t xml:space="preserve">    NDE A B1
 </t>
         </is>
       </c>
@@ -26865,7 +26873,7 @@
     <row r="95">
       <c r="A95" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEC D1
+          <t xml:space="preserve">SEC B1
 </t>
         </is>
       </c>
